--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -46,7 +46,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Must load with no route regression</t>
+          <t>Must load with no route regression; widgets must be clickable</t>
         </is>
       </c>
     </row>
@@ -63,7 +63,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Polished, compact, readable, no horizontal overflow</t>
+          <t>Polished, compact, readable, no horizontal overflow; swipe must work</t>
         </is>
       </c>
     </row>
@@ -155,15 +155,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mobile-safe Notification Center with grouped premium cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Status dock</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</t>
         </is>
@@ -199,10 +216,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -231,10 +263,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Use backend-provided real titles</t>
         </is>
@@ -263,10 +310,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Preserve source URLs</t>
         </is>
@@ -295,10 +357,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Decision-relevance summary</t>
         </is>
@@ -327,10 +404,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Decision-friendly language</t>
         </is>
@@ -359,10 +451,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Confidence framing</t>
         </is>
@@ -381,22 +488,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mobile Settings</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fix empty mobile settings</t>
+          <t>Release Center opens Academy incorrectly</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>HERMES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Useful mobile controls</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Release Center routing mismatch</t>
         </is>
       </c>
     </row>
@@ -413,22 +535,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Workspace Layout</t>
+          <t>Mobile Home</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Draggable dashboard widgets</t>
+          <t>Market Pulse swipe gestures failing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>ATHENA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Local-first layout</t>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Swipe gestures failing</t>
         </is>
       </c>
     </row>
@@ -440,27 +577,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stock Intelligence</t>
+          <t>Home Dashboard</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Analyst Targets widget per stock</t>
+          <t>Home widgets not clickable</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Required per-stock intelligence</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Likely pointer-events/z-index issue</t>
         </is>
       </c>
     </row>
@@ -472,27 +624,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Intelligence Feed</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unified feed sources</t>
+          <t>Mobile stutter and smoothness degradation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Yahoo, Discord, SA, Reuters, PIA, X, IBKR</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Motion/render cost issue</t>
         </is>
       </c>
     </row>
@@ -504,27 +671,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Watchlists</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Add/remove/sort/company logo/mini charts</t>
+          <t>Notification Center responsive failure</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>First-class workspace</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Broken wrapping and mobile invisible state</t>
         </is>
       </c>
     </row>
@@ -541,22 +723,272 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Markets</t>
+          <t>Technical Snapshot</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sector and industry heatmap</t>
+          <t>Expansion</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Macro overview</t>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Support/resistance, AI interpretation, trade scenarios, confidence meter, multi-timeframe modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PIA-BL-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Company Research</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hub refactor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Merge Earnings, Financials, Ratios, Targets inside Company tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PIA-BL-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Videos</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Experience rework</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YouTube-style previews, featured media, thumbnail hierarchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PIA-BL-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Scanner</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Opportunity Board compression</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Compact filter chips, remove oversized sort controls, mobile-first scanner rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PIA-BL-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Notification Center refactor</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Mobile-safe sheet, grouped notifications, premium stacked cards, category identities</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PIA-BL-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Intelligence Cards</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Density refactor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Reduce oversized horizontal cards; compact mobile cards; expandable density system</t>
         </is>
       </c>
     </row>
@@ -597,105 +1029,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mobile-first mock compliance</t>
+          <t>UX direction and mock compliance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Home dashboard, mobile Home, app shell, workspace visibility, status dock</t>
+          <t>Stock workspace improvements, mobile/home refinements, governance updates</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Visible progress toward approved dark premium mocks</t>
+          <t>Implementation branches merged and governance updated</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V3 Foundation</t>
+          <t>Sprint 2C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Workspace platform</t>
+          <t>UAT failure remediation and density pass</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Configurable workspaces with existing widgets</t>
+          <t>Routing mismatch, swipe gestures, widget clickability, performance, Notification Center responsiveness</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Workspace registry and widget catalog remain source of truth</t>
+          <t>Critical UAT failures fixed and mobile interactions stable</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V3 Intelligence</t>
+          <t>V3 Foundation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stock intelligence expansion</t>
+          <t>Workspace platform</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analyst targets, unified feed, per-stock targets</t>
+          <t>Configurable workspaces with existing widgets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Each stock detail has actionable intelligence</t>
+          <t>Workspace registry and widget catalog remain source of truth</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V3 Portfolio Ops</t>
+          <t>V3 Intelligence</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Watchlists and scanner depth</t>
+          <t>Stock intelligence expansion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Watchlist operations, scanner workflows, heatmaps</t>
+          <t>Analyst targets, unified feed, per-stock targets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Workspaces feel operational</t>
+          <t>Each stock detail has actionable intelligence</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V4 Platform</t>
+          <t>V3 Portfolio Ops</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Persistence and backup</t>
+          <t>Watchlists and scanner depth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cloud backup, restore, storage efficiency</t>
+          <t>Watchlist operations, scanner workflows, heatmaps</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reliable local-first with optional sync</t>
+          <t>Workspaces feel operational</t>
         </is>
       </c>
     </row>
@@ -846,12 +1278,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TradingView planned shared chart widget</t>
+          <t>Final stock tab order: Quote, Technical, News, Company, Videos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Avoid fragmented chart implementations</t>
+          <t>Locks navigation model for Sprint 2C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -868,15 +1300,81 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>No backend/API contract changes for visual compliance sprints</t>
+          <t>Company tab absorbs Earnings, Financials, Ratios, and Targets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Keeps design work isolated</t>
+          <t>Reduces tab sprawl while preserving research depth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADR-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical tab owns support/resistance, AI interpretation, scenarios, confidence, and timeframe modes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Keeps actionable trading context in one workspace</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADR-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Videos tab requires media-first previews and thumbnail hierarchy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prevents video intelligence from reading as raw text lists</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADR-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Notification Center must be mobile-safe grouped premium cards</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fixes responsive failure and establishes category identity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
@@ -907,6 +1405,21 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
@@ -929,6 +1442,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Required before commit</t>
         </is>
       </c>
@@ -951,6 +1479,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Required before commit</t>
         </is>
       </c>
@@ -973,6 +1516,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Required before commit</t>
         </is>
       </c>
@@ -995,6 +1553,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Required before commit</t>
         </is>
       </c>
@@ -1017,6 +1590,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Required before commit</t>
         </is>
       </c>
@@ -1039,7 +1627,207 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Required before commit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UAT-011</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Release Center routing mismatch</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Release Center must not open Academy incorrectly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UAT-012</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Market Pulse swipe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Swipe gestures must work on mobile Market Pulse</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UAT-013</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Home widget clickability</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Home widgets must be clickable and not blocked by pointer-events/z-index</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UAT-014</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mobile performance smoothness</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mobile interactions must not stutter from excessive motion/render cost</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UAT-015</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Notification Center responsiveness</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Notification Center must wrap correctly and remain visible on mobile</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1913,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cards/widgets</t>
+          <t>Stock tab order</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dense hierarchy, clear badges, no raw text blocks</t>
+          <t>Quote, Technical, News, Company, Videos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technical Snapshot</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Support/resistance, AI interpretation, trade scenarios, confidence meter, multi-timeframe modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Company Research</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Merge Earnings, Financials, Ratios, Targets inside Company tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Videos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>YouTube-style previews, featured media, thumbnail hierarchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Opportunity Board</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Compact filter chips, remove oversized sort controls, mobile-first scanner rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Notification Center</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mobile-safe sheet, grouped notifications, premium stacked cards, category identities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Intelligence Cards</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Reduce oversized horizontal cards, compact mobile cards, expandable density system</t>
         </is>
       </c>
     </row>
@@ -1191,115 +2051,196 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Merged</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ATHENA</t>
+          <t>HERMES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Add master backlog source of truth artifacts</t>
+          <t>Stock intelligence mock compliance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>feat/pia-v3-foundation-integration</t>
+          <t>feat/v3-stock-mock-compliance-hermes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>docs: add PIA master backlog source of truth</t>
+          <t>feat: improve stock intelligence mock compliance</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Merged</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Future agent</t>
+          <t>ATHENA + HERMES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>News UX V2 implementation</t>
+          <t>Finalize Sprint 2B UX direction and governance updates</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>feat: finalize sprint 2B UX direction and governance updates</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Future agent</t>
+          <t>HERMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analyst Targets widget</t>
+          <t>Fix Release Center routing mismatch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Planned Sprint 2C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Future agent</t>
+          <t>ATHENA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unified Intelligence Feed</t>
+          <t>Fix Market Pulse swipe gestures</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Planned Sprint 2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fix Home widget clickability</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Planned Sprint 2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Reduce mobile performance lag</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Planned Sprint 2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Refactor Notification Center responsiveness</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Planned Sprint 2C</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -683,12 +683,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1726,17 +1726,17 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M233"/>
+  <dimension ref="A1:M235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12437,12 +12437,12 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>HERMES fixed 2026-05-28</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -12918,6 +12918,115 @@
       <c r="I233" t="inlineStr">
         <is>
           <t>Reduce oversized horizontal cards; compact mobile cards; expandable density system</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="12" t="inlineStr">
+        <is>
+          <t>S2C-MOBILE-STABILIZATION</t>
+        </is>
+      </c>
+      <c r="B234" s="12" t="inlineStr">
+        <is>
+          <t>Mobile/Home</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C stabilization</t>
+        </is>
+      </c>
+      <c r="D234" s="12" t="inlineStr">
+        <is>
+          <t>Mobile-critical interaction fixes</t>
+        </is>
+      </c>
+      <c r="E234" s="12" t="inlineStr">
+        <is>
+          <t>Fixed Home click targets, Market Pulse swipe, mobile notification sheet/cards, compact scanner sort controls, and first-pass mobile render cost.</t>
+        </is>
+      </c>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G234" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H234" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I234" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="J234" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="K234" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="L234" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.1</t>
+        </is>
+      </c>
+      <c r="M234" s="12" t="inlineStr">
+        <is>
+          <t>Build and route validation passed; Release Center routing remains with HERMES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>S2C-STOCK-INTEL-REFINEMENT</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Sprint 2C stock workspace refinement</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Technical decision workflow, Company hub, media-first Videos, compact News cards, Release Center routing fix.</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -12954,18 +13063,18 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13442,21 +13551,58 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stock workspace intelligence refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Make stock workspace mobile-first and decision-oriented.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Technical decision workflow; Company fundamentals hub; media-first Videos; compact News; Release Center routing fix.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Build/routes PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14113,21 +14259,48 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ADR-011</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Routing</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Release Center uses explicit #tool=about routing so persisted workspace state cannot reopen Academy.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Fixes Sprint 2C Release Center routing mismatch without changing workspace registry architecture.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14763,12 +14936,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fixed 2026-05-28 via explicit #tool=about routing; route smoke checks pass.</t>
         </is>
       </c>
     </row>
@@ -14917,19 +15095,103 @@
       <c r="G20" t="inlineStr">
         <is>
           <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>UAT-S2C-MOBILE</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Mobile/Home</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Validate mobile interactions and routes</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Home widgets clickable; Market Pulse swipes; bell opens mobile-safe notification sheet; scanner controls compact; privacy mode preserved; routes return 200.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>npm run build passed; /, /mobile, and /setup returned 200. Real-device performance profiling remains recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UAT-S2C-STOCK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Stock Workspace</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Validate locked tab order, Technical decision workflow, Company hub, Videos last, compact News cards, Release Center routing, and routes.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Build passes; /, /mobile, /setup return 200; Release Center opens about tool route.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>npm run build passed. Interactive browser console not available; route smoke checks passed.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -15292,18 +15554,18 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15895,10 +16157,94 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>TASK-S2C-MOBILE-STABILIZATION</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + ARTEMIS</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Mobile-first stabilization</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Home interactions, Market Pulse swipe, Notification Center bottom sheet, stacked notification cards, compact scanner controls, and performance smoothing.</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Build passed; routes 200</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>HERMES keeps Release Center routing mismatch; profile mobile performance on device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TASK-S2C-STOCK-INTEL-REFINEMENT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stock workspace intelligence refinement</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Quote/Technical/News/Company/Videos tabs, trade-entry Technical workflow, About/Fundamentals Company hub, media-first Videos, compact News, Release Center routing.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Build passed; routes 200</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Live fundamentals/targets provider integration remains future work.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15909,7 +16255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -15980,7 +16326,7 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FIXED 2026-05-28</t>
         </is>
       </c>
     </row>
@@ -16101,6 +16447,30 @@
       <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Mobile-first investment operating system</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C mobile stabilization</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-28: Home clickability, Market Pulse swipe, mobile Notification Center, compact scanner controls, and first-pass performance smoothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sprint 2C stock workspace refinement</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-28: locked tabs, Technical decision workflow, Company hub, Videos last, compact News, Release Center routing fix.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M235"/>
+  <dimension ref="A1:M236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13027,6 +13027,73 @@
       <c r="H235" t="inlineStr">
         <is>
           <t>2026-05-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="12" t="inlineStr">
+        <is>
+          <t>DESIGN-GOV-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B236" s="12" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first design governance system</t>
+        </is>
+      </c>
+      <c r="E236" s="12" t="inlineStr">
+        <is>
+          <t>Created locked design-system docs and mock storage hierarchy. UI implementation now requires approved mock, design-system rule, mobile-first principle, and changelog reference.</t>
+        </is>
+      </c>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G236" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H236" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="I236" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="J236" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="K236" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="L236" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.5</t>
+        </is>
+      </c>
+      <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio Snapshot redesign is blocked until approved mobile mock.</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13585,6 +13652,43 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>Build/routes PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Lock mock-first workflow before further UI implementation</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Design-system docs; mock folders; mandatory PO review gate; Portfolio Snapshot mobile mock gate</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first gate required before UI changes</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14283,6 +14387,33 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>Fixes Sprint 2C Release Center routing mismatch without changing workspace registry architecture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>DEC-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first development is mandatory before UI implementation</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>No widget, screen, workspace, navigation change, or major refactor may be implemented before mock creation, PO review, corrections, APPROVED status, and storage in docs/design-system/mocks/.</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15548,6 +15679,33 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>Reduce oversized horizontal cards, compact mobile cards, expandable density system</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>MOCK-GOV-001</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first governance</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Approved mocks are mandatory implementation references and must live under docs/design-system/mocks/.</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio Snapshot requires approved mobile mock before redesign.</t>
         </is>
       </c>
     </row>
@@ -15565,7 +15723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16241,6 +16399,48 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>TASK-DESIGN-GOV-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Design governance + mock-first workflow</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Create design-system docs, mock directories, mandatory mock-first rules, Portfolio Snapshot gate, and governance updates.</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Docs diff/check clean</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>Use approved mocks before further UI implementation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -16255,7 +16455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16474,6 +16674,18 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-05-28: Mock-first development is mandatory; approved mocks must be stored under docs/design-system/mocks/ before UI implementation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M236"/>
+  <dimension ref="A1:M237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13092,6 +13092,73 @@
         </is>
       </c>
       <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio Snapshot redesign is blocked until approved mobile mock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="12" t="inlineStr">
+        <is>
+          <t>DESIGN-GOV-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B237" s="12" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="D237" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first design governance system</t>
+        </is>
+      </c>
+      <c r="E237" s="12" t="inlineStr">
+        <is>
+          <t>Created locked design-system docs and mock storage hierarchy. UI implementation now requires approved mock, design-system rule, mobile-first principle, and changelog reference.</t>
+        </is>
+      </c>
+      <c r="F237" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H237" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="I237" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="J237" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="K237" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="L237" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.5</t>
+        </is>
+      </c>
+      <c r="M237" s="12" t="inlineStr">
         <is>
           <t>Portfolio Snapshot redesign is blocked until approved mobile mock.</t>
         </is>
@@ -13141,7 +13208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13687,6 +13754,43 @@
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first gate required before UI changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Lock mock-first workflow before further UI implementation</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Design-system docs; mock folders; mandatory PO review gate; Portfolio Snapshot mobile mock gate</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Mock-first gate required before UI changes</t>
         </is>
@@ -13706,7 +13810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14412,6 +14516,33 @@
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>No widget, screen, workspace, navigation change, or major refactor may be implemented before mock creation, PO review, corrections, APPROVED status, and storage in docs/design-system/mocks/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>DEC-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first development is mandatory before UI implementation</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>No widget, screen, workspace, navigation change, or major refactor may be implemented before mock creation, PO review, corrections, APPROVED status, and storage in docs/design-system/mocks/.</t>
         </is>
@@ -15327,7 +15458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15704,6 +15835,33 @@
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio Snapshot requires approved mobile mock before redesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MOCK-GOV-001</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Mock-first governance</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Approved mocks are mandatory implementation references and must live under docs/design-system/mocks/.</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Portfolio Snapshot requires approved mobile mock before redesign.</t>
         </is>
@@ -15723,7 +15881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -16441,6 +16599,48 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>TASK-DESIGN-GOV-MOCK-FIRST</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>ATHENA + HERMES</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Design governance + mock-first workflow</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Create design-system docs, mock directories, mandatory mock-first rules, Portfolio Snapshot gate, and governance updates.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Docs diff/check clean</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Use approved mocks before further UI implementation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -16455,7 +16655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16686,6 +16886,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Design Governance</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-05-28: Mock-first development is mandatory; approved mocks must be stored under docs/design-system/mocks/ before UI implementation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1736,7 +1736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M237"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13161,6 +13161,73 @@
       <c r="M237" s="12" t="inlineStr">
         <is>
           <t>Portfolio Snapshot redesign is blocked until approved mobile mock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="12" t="inlineStr">
+        <is>
+          <t>DATA-HYBRID-MOCK-LAYER</t>
+        </is>
+      </c>
+      <c r="B238" s="12" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="C238" s="12" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="D238" s="12" t="inlineStr">
+        <is>
+          <t>Hybrid mock intelligence data layer</t>
+        </is>
+      </c>
+      <c r="E238" s="12" t="inlineStr">
+        <is>
+          <t>Created backend/mock_intelligence_data.py with Bloomberg-lite mock data for NVDA, AMD, SOFI, IREN, AVAV, GOOGL, TSLA, CRWV, NBIS. Includes company profile, financials, ratios, earnings, analyst targets, and technical levels. Integrated into /stock/{ticker} intelligence response. IREN added to positions; AVAV+TSLA added to watchlist. Live news/videos preserved.</t>
+        </is>
+      </c>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G238" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H238" s="12" t="inlineStr">
+        <is>
+          <t>HEPHAESTUS + APOLLO</t>
+        </is>
+      </c>
+      <c r="I238" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="J238" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="K238" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="L238" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.6</t>
+        </is>
+      </c>
+      <c r="M238" s="12" t="inlineStr">
+        <is>
+          <t>Mock prices calibrated to 2026-05-28. Live IBKR or Yahoo needed for real-time prices.</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13793,6 +13860,43 @@
       <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Mock-first gate required before UI changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2C</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Deploy hybrid mock intelligence data for UI evaluation</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>backend/mock_intelligence_data.py; state.py IREN+AVAV+TSLA; stock_intelligence.py merge</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>HEPHAESTUS + APOLLO</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Live news/videos preserved; mock used for fundamentals and technicals only</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -16898,6 +17002,18 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-28: Hybrid mock intelligence data layer v0.3.6 deployed. 9 tickers with company, fundamentals, ratios, earnings, targets, technical levels. IREN in positions, AVAV+TSLA in watchlist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -16759,7 +16759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17014,6 +17014,18 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Runtime Governance</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-05-28 (v0.3.15): Single Next Dev Server Rule — only one Next dev server may run; check port 3000 first; kill stale node/next/npm and delete frontend/.next before restart; start LAN-bound (npm run dev -- -H 0.0.0.0); never run npm run build against a live dev server's .next; unstyled mobile = suspect stale/corrupt .next (404 CSS chunk), not UI code.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1717,6 +1717,28 @@
       <c r="C68" t="inlineStr">
         <is>
           <t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.15</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Workspace Manager + Custom Workspaces</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Implemented 2026-05-28</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Mobile hamburger manager, direct overflow workspace open, Settings/About access, configurable pinned bottom nav, desktop sidebar parity, custom local workspaces.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17026,6 +17048,30 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Workspace Manager</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Workspace Manager</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; Settings/About are accessible; all/overflow workspaces can open directly; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -16781,7 +16781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17072,6 +17072,18 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Mobile Regression Fix</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>DONE 2026-05-28 (v0.3.16): Global search universe expanded (AAPL/MSFT/AMZN/META/SPY/QQQ/+ v0.3.6 set) with Enter-to-open and Analyze fallback; per-ticker mock news fallback (generate_mock_news) so every symbol shows source-badged news; used_demo only true for demo/mock, false for real Yahoo. Hamburger menu satisfied by v0.3.15 Workspace Manager.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BacklogTable" displayName="BacklogTable" ref="A1:M216" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BacklogTable" displayName="BacklogTable" ref="A1:M240" headerRowCount="1">
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Category"/>
@@ -683,1082 +683,1082 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:D69"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="14" customWidth="1" min="1" max="1"/>
+    <ns0:col width="28" customWidth="1" min="2" max="2"/>
+    <ns0:col width="72" customWidth="1" min="3" max="3"/>
+    <ns0:col width="10" customWidth="1" min="4" max="4"/>
+    <ns0:col width="18" customWidth="1" min="5" max="5"/>
+    <ns0:col width="18" customWidth="1" min="6" max="6"/>
+    <ns0:col width="28" customWidth="1" min="8" max="8"/>
+    <ns0:col width="10" customWidth="1" min="9" max="9"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="21" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PIA Master Backlog Dashboard</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="n"/>
+      <ns0:c r="C1" s="1" t="n"/>
+      <ns0:c r="D1" s="1" t="n"/>
+      <ns0:c r="E1" s="1" t="n"/>
+      <ns0:c r="F1" s="1" t="n"/>
+      <ns0:c r="G1" s="1" t="n"/>
+      <ns0:c r="H1" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="25" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Generated: 2026-05-27 14:35 | Source of truth snapshot for project management</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="n"/>
+      <ns0:c r="C2" s="1" t="n"/>
+      <ns0:c r="D2" s="1" t="n"/>
+      <ns0:c r="E2" s="1" t="n"/>
+      <ns0:c r="F2" s="1" t="n"/>
+      <ns0:c r="G2" s="1" t="n"/>
+      <ns0:c r="H2" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="3"/>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Metric</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Value</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Notes</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Priority</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Count</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Category</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I4" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Items</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Total backlog items</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="12" t="n">
+        <ns0:v>215</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>All rows in Backlog sheet</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F5" t="n">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="H5" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Academy</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I5" s="12" t="n">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0 items</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="12" t="n">
+        <ns0:v>42</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Critical / foundational</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" t="n">
+        <ns0:v>112</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Portfolio</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="12" t="n">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P1 items</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B7" s="12" t="n">
+        <ns0:v>112</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>High priority</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F7" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Earnings</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I7" s="12" t="n">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Done / Approved</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B8" s="12" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="C8" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Delivered and approved</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H8" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Integrations</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" s="12" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Tech Pass / UAT pending</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B9" s="12" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Needs UAT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H9" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Markets &amp; Macro</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I9" s="12" t="n">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Planned</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B10" s="12" t="n">
+        <ns0:v>148</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Future work</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H10" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Alerts</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I10" s="12" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>New bugs/items</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B11" s="12" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Newly captured</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H11" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Backend</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I11" s="12" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="E12" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Status</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F12" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Count</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H12" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mobile</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I12" s="12" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="E13" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DONE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F13" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="H13" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Notes</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I13" s="12" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="6" t="n"/>
+      <ns0:c r="B14" s="6" t="n"/>
+      <ns0:c r="C14" s="6" t="n"/>
+      <ns0:c r="D14" s="6" t="n"/>
+      <ns0:c r="E14" t="inlineStr">
+        <ns0:is>
+          <ns0:t>FOUNDATION DONE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F14" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Workspace</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I14" s="12" t="n">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="12" t="n"/>
+      <ns0:c r="B15" s="12" t="n"/>
+      <ns0:c r="C15" s="12" t="n"/>
+      <ns0:c r="D15" s="12" t="n"/>
+      <ns0:c r="E15" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TECH PASS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F15" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="H15" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Scanner</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I15" s="12" t="n">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16" s="12" t="n"/>
+      <ns0:c r="B16" s="12" t="n"/>
+      <ns0:c r="C16" s="12" t="n"/>
+      <ns0:c r="D16" s="12" t="n"/>
+      <ns0:c r="E16" t="inlineStr">
+        <ns0:is>
+          <ns0:t>IN PROGRESS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F16" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="H16" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Backup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I16" s="12" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="A17" s="12" t="n"/>
+      <ns0:c r="B17" s="12" t="n"/>
+      <ns0:c r="C17" s="12" t="n"/>
+      <ns0:c r="D17" s="12" t="n"/>
+      <ns0:c r="E17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NEW</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F17" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="H17" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Command</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I17" s="12" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="A18" s="12" t="n"/>
+      <ns0:c r="B18" s="12" t="n"/>
+      <ns0:c r="C18" s="12" t="n"/>
+      <ns0:c r="D18" s="12" t="n"/>
+      <ns0:c r="E18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>PLANNED</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F18" t="n">
+        <ns0:v>148</ns0:v>
+      </ns0:c>
+      <ns0:c r="H18" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Performance</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I18" s="12" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="A19" s="12" t="n"/>
+      <ns0:c r="B19" s="12" t="n"/>
+      <ns0:c r="C19" s="12" t="n"/>
+      <ns0:c r="D19" s="12" t="n"/>
+      <ns0:c r="E19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ENVIRONMENT</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F19" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="H19" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Settings</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I19" s="12" t="n">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="20">
+      <ns0:c r="H20" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AI Core</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I20" s="12" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="21">
+      <ns0:c r="H21" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>AI Infrastructure</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I21" s="12" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="22">
+      <ns0:c r="A22" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>When</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B22" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Action</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C22" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Description</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D22" s="6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Priority</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H22" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Crypto</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I22" s="12" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="23">
+      <ns0:c r="A23" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Now</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B23" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sprint 2B Mock Compliance</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C23" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Athena: mobile-first Home mock compliance; Hermes: stock/news/videos mock compliance.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D23" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H23" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Discord</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I23" s="12" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="24">
+      <ns0:c r="A24" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Next</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B24" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UAT after preview/local</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C24" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UAT must be mock-compliance, not only load/no crash.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D24" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H24" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Trade Coach</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I24" s="12" t="n">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="25">
+      <ns0:c r="A25" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DONE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B25" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Backlog/Git file update</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C25" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Commit XLSX + markdown/JSON source-of-truth into repo.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D25" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H25" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Watchlists</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I25" s="12" t="n">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="26">
+      <ns0:c r="A26" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Later</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B26" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Vercel mobile preview</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C26" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Branch preview URLs for mobile UAT.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D26" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H26" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Bug</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I26" s="12" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="27">
+      <ns0:c r="A27" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Later</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B27" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Portfolio V3 MVP</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C27" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>My Portfolio with snapshots, heatmap, attribution, targets, intelligence.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D27" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H27" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Voice</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I27" s="12" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="28">
+      <ns0:c r="A28" s="12" t="n"/>
+      <ns0:c r="B28" s="12" t="n"/>
+      <ns0:c r="H28" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Foundation</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I28" s="12" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="29">
+      <ns0:c r="A29" s="12" t="n"/>
+      <ns0:c r="B29" s="12" t="n"/>
+      <ns0:c r="H29" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Sources</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I29" s="12" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="30">
+      <ns0:c r="A30" s="12" t="n"/>
+      <ns0:c r="B30" s="12" t="n"/>
+      <ns0:c r="H30" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>DevOps</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I30" s="12" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="31">
+      <ns0:c r="A31" s="12" t="n"/>
+      <ns0:c r="B31" s="12" t="n"/>
+      <ns0:c r="H31" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Stock Workspace</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I31" s="12" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="32">
+      <ns0:c r="A32" s="12" t="n"/>
+      <ns0:c r="B32" s="12" t="n"/>
+      <ns0:c r="H32" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Change</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I32" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="33">
+      <ns0:c r="A33" s="12" t="n"/>
+      <ns0:c r="B33" s="12" t="n"/>
+      <ns0:c r="H33" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Design System</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I33" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="34">
+      <ns0:c r="A34" s="12" t="n"/>
+      <ns0:c r="B34" s="12" t="n"/>
+      <ns0:c r="H34" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Heatmap</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I34" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="35">
+      <ns0:c r="A35" s="12" t="n"/>
+      <ns0:c r="B35" s="12" t="n"/>
+      <ns0:c r="H35" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>News</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I35" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="36">
+      <ns0:c r="A36" s="12" t="n"/>
+      <ns0:c r="B36" s="12" t="n"/>
+      <ns0:c r="H36" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Process</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I36" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="37">
+      <ns0:c r="A37" s="12" t="n"/>
+      <ns0:c r="B37" s="12" t="n"/>
+      <ns0:c r="H37" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Stock Intelligence</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I37" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="38">
+      <ns0:c r="A38" s="12" t="n"/>
+      <ns0:c r="B38" s="12" t="n"/>
+      <ns0:c r="H38" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UI/UX</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I38" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="39">
+      <ns0:c r="A39" s="12" t="n"/>
+      <ns0:c r="B39" s="12" t="n"/>
+      <ns0:c r="H39" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>UX</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I39" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="40">
+      <ns0:c r="A40" s="12" t="n"/>
+      <ns0:c r="B40" s="12" t="n"/>
+      <ns0:c r="H40" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Widgets</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I40" s="12" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="41">
+      <ns0:c r="A41" s="12" t="n"/>
+      <ns0:c r="B41" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="42">
+      <ns0:c r="A42" s="12" t="n"/>
+      <ns0:c r="B42" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="43">
+      <ns0:c r="A43" s="12" t="n"/>
+      <ns0:c r="B43" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="44">
+      <ns0:c r="A44" s="12" t="n"/>
+      <ns0:c r="B44" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="45">
+      <ns0:c r="A45" s="12" t="n"/>
+      <ns0:c r="B45" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="46">
+      <ns0:c r="A46" s="12" t="n"/>
+      <ns0:c r="B46" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="47">
+      <ns0:c r="A47" s="12" t="n"/>
+      <ns0:c r="B47" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="48">
+      <ns0:c r="A48" s="12" t="n"/>
+      <ns0:c r="B48" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="49">
+      <ns0:c r="A49" s="12" t="n"/>
+      <ns0:c r="B49" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="50">
+      <ns0:c r="A50" s="12" t="n"/>
+      <ns0:c r="B50" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="51">
+      <ns0:c r="A51" s="12" t="n"/>
+      <ns0:c r="B51" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="52">
+      <ns0:c r="A52" s="12" t="n"/>
+      <ns0:c r="B52" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="53">
+      <ns0:c r="A53" s="12" t="n"/>
+      <ns0:c r="B53" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="54">
+      <ns0:c r="A54" s="12" t="n"/>
+      <ns0:c r="B54" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="55">
+      <ns0:c r="A55" s="12" t="n"/>
+      <ns0:c r="B55" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="56">
+      <ns0:c r="A56" s="12" t="n"/>
+      <ns0:c r="B56" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="57">
+      <ns0:c r="A57" s="12" t="n"/>
+      <ns0:c r="B57" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="58">
+      <ns0:c r="A58" s="12" t="n"/>
+      <ns0:c r="B58" s="12" t="n"/>
+    </ns0:row>
+    <ns0:row r="59">
+      <ns0:c r="A59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Route</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Purpose</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C59" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Validation Expectation</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="60">
+      <ns0:c r="A60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>/</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Home dashboard and desktop workspace shell</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C60" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Must load with no route regression; widgets must be clickable</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="61">
+      <ns0:c r="A61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>/mobile</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mobile-first command experience</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C61" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Polished, compact, readable, no horizontal overflow; swipe must work</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="62">
+      <ns0:c r="A62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>/setup</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Setup and onboarding flow</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C62" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Must remain preserved</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="63">
+      <ns0:c r="A63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Priority</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Area</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C63" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Requirement</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="64">
+      <ns0:c r="A64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Home dashboard</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C64" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Premium visual identity while preserving working widgets</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="65">
+      <ns0:c r="A65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mobile Home</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C65" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Must not feel like squeezed desktop</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="66">
+      <ns0:c r="A66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Privacy mode</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C66" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Amount hiding must remain intact</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="67">
+      <ns0:c r="A67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P0</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Notifications</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C67" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mobile-safe Notification Center with grouped premium cards</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="68">
+      <ns0:c r="A68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>P1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Status dock</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C68" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="69">
+      <ns0:c r="A69" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>v0.3.15</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B69" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Workspace Manager + Custom Workspaces</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C69" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Implemented 2026-05-28</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D69" s="12" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Mobile hamburger manager, direct overflow workspace open, Settings/About access, configurable pinned bottom nav, desktop sidebar parity, custom local workspaces.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:mergeCells count="2">
+    <ns0:mergeCell ref="A2:H2"/>
+    <ns0:mergeCell ref="A1:H1"/>
+  </ns0:mergeCells>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:drawing ns1:id="rId1"/>
+</ns0:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>PIA Master Backlog Dashboard</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Generated: 2026-05-27 14:35 | Source of truth snapshot for project management</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Items</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Total backlog items</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>All rows in Backlog sheet</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>42</v>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>Academy</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>P0 items</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Critical / foundational</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>112</v>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>Portfolio</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>P1 items</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>High priority</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>Earnings</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Done / Approved</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Delivered and approved</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>Integrations</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Tech Pass / UAT pending</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Needs UAT</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Markets &amp; Macro</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>148</v>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Future work</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>Alerts</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>New bugs/items</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Newly captured</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>Mobile</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>FOUNDATION DONE</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>Workspace</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TECH PASS</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>Scanner</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>Backup</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>148</v>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ENVIRONMENT</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>AI Core</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>AI Infrastructure</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Sprint 2B Mock Compliance</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Athena: mobile-first Home mock compliance; Hermes: stock/news/videos mock compliance.</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Next</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>UAT after preview/local</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>UAT must be mock-compliance, not only load/no crash.</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>Trade Coach</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Next</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>Backlog/Git file update</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Commit XLSX + markdown/JSON source-of-truth into repo.</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>Vercel mobile preview</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Branch preview URLs for mobile UAT.</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Later</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Portfolio V3 MVP</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>My Portfolio with snapshots, heatmap, attribution, targets, intelligence.</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>Foundation</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="H31" s="12" t="inlineStr">
-        <is>
-          <t>Stock Workspace</t>
-        </is>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>Change</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>Design System</t>
-        </is>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>Heatmap</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="H35" s="12" t="inlineStr">
-        <is>
-          <t>News</t>
-        </is>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>Widgets</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="n"/>
-      <c r="B44" s="12" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="n"/>
-      <c r="B47" s="12" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="n"/>
-      <c r="B48" s="12" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="n"/>
-      <c r="B49" s="12" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="n"/>
-      <c r="B50" s="12" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="12" t="n"/>
-      <c r="B51" s="12" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="n"/>
-      <c r="B52" s="12" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="n"/>
-      <c r="B53" s="12" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="12" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="12" t="n"/>
-      <c r="B55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="n"/>
-      <c r="B56" s="12" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="12" t="n"/>
-      <c r="B57" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="n"/>
-      <c r="B58" s="12" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Validation Expectation</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Home dashboard and desktop workspace shell</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Must load with no route regression; widgets must be clickable</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>/mobile</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Mobile-first command experience</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Polished, compact, readable, no horizontal overflow; swipe must work</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>/setup</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Setup and onboarding flow</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Must remain preserved</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Home dashboard</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Premium visual identity while preserving working widgets</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Mobile Home</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Must not feel like squeezed desktop</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Privacy mode</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Amount hiding must remain intact</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Notifications</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Mobile-safe Notification Center with grouped premium cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Status dock</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="12" t="inlineStr">
-        <is>
-          <t>v0.3.15</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>Workspace Manager + Custom Workspaces</t>
-        </is>
-      </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Implemented 2026-05-28</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>Mobile hamburger manager, direct overflow workspace open, Settings/About access, configurable pinned bottom nav, desktop sidebar parity, custom local workspaces.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2497,54 +2497,70 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="12" spans="1:13">
+      <c r="A12" t="inlineStr">
         <is>
           <t>PIA-BUG-027</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Dead Controls</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Watch / Set alert / Risk check dead controls</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Controls must be implemented or marked disabled/coming soon with honest tooltip/state.</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>UNASSIGNED</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="str"/>
-      <c r="J12" s="12" t="str"/>
-      <c r="K12" s="12" t="str"/>
-      <c r="L12" s="12" t="str"/>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>Trust issue.</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Workspace Layout</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Custom Workspaces Lose Widgets</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Custom workspace template widgets are filtered out because normalizeWorkspaceLayout intersects saved widgets with supportedWorkspaces, and custom workspace ids match no catalog widget.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PIA-ARCH-001-C</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SPEC READY</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Fix defined in docs/PIA_WORKSPACE_ARCHITECTURE_FINAL.md. Keep open until implementation and validation.</t>
         </is>
       </c>
     </row>
@@ -13250,6 +13266,140 @@
       <c r="M238" s="12" t="inlineStr">
         <is>
           <t>Mock prices calibrated to 2026-05-28. Live IBKR or Yahoo needed for real-time prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" spans="1:13">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PIA-UX-032</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Portfolio Mobile</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Portfolio Mobile Card V2</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Mobile portfolio card V2 release reference and workbook sync after Markdown governance update.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>v0.3.18 Portfolio Mobile Card V2</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>Closed 2026-05-30. Owner ARTEMIS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" spans="1:13">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PIA-UX-033</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Workspace System</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Workspace Architecture Implementation</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Future Workspace system implementation tracked against the final architecture source of truth.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>ATHENA / Architecture</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>PIA-ARCH-001-FINAL</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>SPEC READY</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>Architecture source: docs/PIA_WORKSPACE_ARCHITECTURE_FINAL.md.</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13436,7 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart ns1:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -16781,7 +16931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17084,6 +17234,18 @@
         </is>
       </c>
     </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Release Reference</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>v0.3.18 Portfolio Mobile Card V2: PIA-UX-032 DONE 2026-05-30. Owner ARTEMIS.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Architecture Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UAT Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approved Mocks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agent Tasks" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CURRENT_STATE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" ns1:id="rId1"/>
+    <sheet name="Backlog" sheetId="2" state="visible" ns1:id="rId2"/>
+    <sheet name="Roadmap" sheetId="3" state="visible" ns1:id="rId3"/>
+    <sheet name="Architecture Decisions" sheetId="4" state="visible" ns1:id="rId4"/>
+    <sheet name="UAT Log" sheetId="5" state="visible" ns1:id="rId5"/>
+    <sheet name="Approved Mocks" sheetId="6" state="visible" ns1:id="rId6"/>
+    <sheet name="Agent Tasks" sheetId="7" state="visible" ns1:id="rId7"/>
+    <sheet name="CURRENT_STATE" sheetId="8" state="visible" ns1:id="rId8"/>
+    <sheet name="UX_IMPROVEMENTS" sheetId="9" ns1:id="rId11"/>
+    <sheet name="CHANGELOG" sheetId="10" ns1:id="rId12"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -1752,13 +1754,108 @@
 </ns0:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C1">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D1">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2">
+        <is>
+          <t>230acdc</t>
+        </is>
+      </c>
+      <c r="C2">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="D2">
+        <is>
+          <t>Watchlist unified column manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
+      <c r="C3">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="D3">
+        <is>
+          <t>Watchlists Mobile V1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B4">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
+      <c r="C4">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="D4">
+        <is>
+          <t>Stock Intelligence data recovery attempt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M240"/>
+  <dimension ref="A1:M265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13400,6 +13497,306 @@
       <c r="M240" t="inlineStr">
         <is>
           <t>Architecture source: docs/PIA_WORKSPACE_ARCHITECTURE_FINAL.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <is>
+          <t>PIA-WL-008</t>
+        </is>
+      </c>
+      <c r="G241">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <is>
+          <t>PIA-WL-009</t>
+        </is>
+      </c>
+      <c r="G242">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <is>
+          <t>PIA-WL-010</t>
+        </is>
+      </c>
+      <c r="G243">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <is>
+          <t>PIA-WL-011</t>
+        </is>
+      </c>
+      <c r="G244">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <is>
+          <t>PIA-WL-012</t>
+        </is>
+      </c>
+      <c r="G245">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <is>
+          <t>PIA-WL-013</t>
+        </is>
+      </c>
+      <c r="G246">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <is>
+          <t>PIA-WL-014</t>
+        </is>
+      </c>
+      <c r="G247">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <is>
+          <t>PIA-SHARED-001</t>
+        </is>
+      </c>
+      <c r="G248">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <is>
+          <t>PIA-SHARED-002</t>
+        </is>
+      </c>
+      <c r="G249">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <is>
+          <t>PIA-SI-001</t>
+        </is>
+      </c>
+      <c r="G250">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <is>
+          <t>PIA-SI-002</t>
+        </is>
+      </c>
+      <c r="G251">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <is>
+          <t>PIA-SI-003</t>
+        </is>
+      </c>
+      <c r="G252">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <is>
+          <t>PIA-SI-004</t>
+        </is>
+      </c>
+      <c r="G253">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <is>
+          <t>PIA-SI-005</t>
+        </is>
+      </c>
+      <c r="G254">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <is>
+          <t>PIA-SI-006</t>
+        </is>
+      </c>
+      <c r="G255">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <is>
+          <t>PIA-SI-007</t>
+        </is>
+      </c>
+      <c r="G256">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <is>
+          <t>PIA-SI-008</t>
+        </is>
+      </c>
+      <c r="G257">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <is>
+          <t>PIA-SI-009</t>
+        </is>
+      </c>
+      <c r="G258">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <is>
+          <t>PIA-SI-010</t>
+        </is>
+      </c>
+      <c r="G259">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <is>
+          <t>PIA-SI-011</t>
+        </is>
+      </c>
+      <c r="G260">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <is>
+          <t>PIA-SI-012</t>
+        </is>
+      </c>
+      <c r="G261">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <is>
+          <t>PIA-SI-013</t>
+        </is>
+      </c>
+      <c r="G262">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <is>
+          <t>PIA-SI-014</t>
+        </is>
+      </c>
+      <c r="G263">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <is>
+          <t>PIA-SI-015</t>
+        </is>
+      </c>
+      <c r="G264">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <is>
+          <t>PIA-SI-016</t>
+        </is>
+      </c>
+      <c r="G265">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -14833,12 +15230,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15720,10 +16117,367 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C23">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D23">
+        <is>
+          <t>Long press Open Chart opens wrong destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C24">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D24">
+        <is>
+          <t>Add To Watchlist non-functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C25">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D25">
+        <is>
+          <t>AI Coach non-functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C26">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D26">
+        <is>
+          <t>Add Instrument stays permanently open</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C27">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D27">
+        <is>
+          <t>Table sorting not working</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C28">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D28">
+        <is>
+          <t>Column catalog limited</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C29">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D29">
+        <is>
+          <t>Key metrics N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C30">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D30">
+        <is>
+          <t>Today Range missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C31">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D31">
+        <is>
+          <t>News empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C32">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D32">
+        <is>
+          <t>Financials unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C33">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D33">
+        <is>
+          <t>Analysis placeholders</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C34">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D34">
+        <is>
+          <t>Analysis label overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C35">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D35">
+        <is>
+          <t>Financial label overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C36">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D36">
+        <is>
+          <t>Options tab placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C37">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D37">
+        <is>
+          <t>Three-dot menu inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C38">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D38">
+        <is>
+          <t>Privacy action missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C39">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D39">
+        <is>
+          <t>Targets not in Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C40">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D40">
+        <is>
+          <t>Chart/Analysis disconnected</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C41">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D41">
+        <is>
+          <t>Manual Holdings search reports backend unavailable</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C42">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D42">
+        <is>
+          <t>Watchlist search affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C43">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D43">
+        <is>
+          <t>Search icon affected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart ns1:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17249,4 +18003,107 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <is>
+          <t>UX-001</t>
+        </is>
+      </c>
+      <c r="B2">
+        <is>
+          <t>Move analyst targets into Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <is>
+          <t>UX-002</t>
+        </is>
+      </c>
+      <c r="B3">
+        <is>
+          <t>Remove Options tab until functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <is>
+          <t>UX-003</t>
+        </is>
+      </c>
+      <c r="B4">
+        <is>
+          <t>Replace ON/OFF buttons with mobile switches</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <is>
+          <t>UX-004</t>
+        </is>
+      </c>
+      <c r="B5">
+        <is>
+          <t>Auto-close Add Instrument after success</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <is>
+          <t>UX-005</t>
+        </is>
+      </c>
+      <c r="B6">
+        <is>
+          <t>Source + relative time on news</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <is>
+          <t>UX-006</t>
+        </is>
+      </c>
+      <c r="B7">
+        <is>
+          <t>One-hand mobile interaction improvements</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <is>
+          <t>UX-007</t>
+        </is>
+      </c>
+      <c r="B8">
+        <is>
+          <t>Unify Customize Metrics with Manage Columns pattern</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -15235,7 +15235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16471,6 +16471,424 @@
       <c r="D43">
         <is>
           <t>Search icon affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C44">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D44">
+        <is>
+          <t>Long Press → Open Chart opens wrong destination</t>
+        </is>
+      </c>
+      <c r="H44">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C45">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D45">
+        <is>
+          <t>Add To Watchlist does not show available lists</t>
+        </is>
+      </c>
+      <c r="H45">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C46">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D46">
+        <is>
+          <t>AI Coach does not perform actions</t>
+        </is>
+      </c>
+      <c r="H46">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C47">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D47">
+        <is>
+          <t>Add ticker field stays permanently open</t>
+        </is>
+      </c>
+      <c r="H47">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C48">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D48">
+        <is>
+          <t>Table sorting (LAST/CHNG/CHG%/VLM) not working</t>
+        </is>
+      </c>
+      <c r="H48">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C49">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D49">
+        <is>
+          <t>Watchlist columns insufficient (missing financial metrics)</t>
+        </is>
+      </c>
+      <c r="H49">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C50">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D50">
+        <is>
+          <t>News tab empty for NVDA</t>
+        </is>
+      </c>
+      <c r="H50">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C51">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D51">
+        <is>
+          <t>Estimate vs Actual overlaps Earnings</t>
+        </is>
+      </c>
+      <c r="H51">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C52">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D52">
+        <is>
+          <t>Analysis labels overlap on mobile</t>
+        </is>
+      </c>
+      <c r="H52">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C53">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D53">
+        <is>
+          <t>Key Metrics show N/A (Open/DayHigh/DayLow/Volume/AvgVolume)</t>
+        </is>
+      </c>
+      <c r="H53">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C54">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D54">
+        <is>
+          <t>Financial sections unavailable</t>
+        </is>
+      </c>
+      <c r="H54">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C55">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D55">
+        <is>
+          <t>Analysis still contains mock content</t>
+        </is>
+      </c>
+      <c r="H55">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C56">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D56">
+        <is>
+          <t>Options tab placeholder should be removed</t>
+        </is>
+      </c>
+      <c r="H56">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C57">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D57">
+        <is>
+          <t>Three-dot menu (⋮) inactive</t>
+        </is>
+      </c>
+      <c r="H57">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C58">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D58">
+        <is>
+          <t>Privacy toggle missing from UI</t>
+        </is>
+      </c>
+      <c r="H58">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C59">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D59">
+        <is>
+          <t>Targets not shown in Overview</t>
+        </is>
+      </c>
+      <c r="H59">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C60">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D60">
+        <is>
+          <t>Manual Holdings: Instrument search reports backend unreachable</t>
+        </is>
+      </c>
+      <c r="H60">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C61">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D61">
+        <is>
+          <t>Watchlist Add Instrument search affected</t>
+        </is>
+      </c>
+      <c r="H61">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="C62">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D62">
+        <is>
+          <t>Search icon/ticker search failing</t>
+        </is>
+      </c>
+      <c r="H62">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -13511,6 +13511,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B241">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D241">
+        <is>
+          <t>Manage Columns uses buttons instead of switches</t>
+        </is>
+      </c>
+      <c r="F241">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H241">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M241">
+        <is>
+          <t>230acdc</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242">
@@ -13523,6 +13548,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B242">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D242">
+        <is>
+          <t>Open Chart opens wrong destination</t>
+        </is>
+      </c>
+      <c r="F242">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H242">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M242">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243">
@@ -13535,6 +13585,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B243">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D243">
+        <is>
+          <t>Add To Watchlist does nothing (lists not shown)</t>
+        </is>
+      </c>
+      <c r="F243">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H243">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M243">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244">
@@ -13547,6 +13622,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B244">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D244">
+        <is>
+          <t>AI Coach inactive</t>
+        </is>
+      </c>
+      <c r="F244">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H244">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M244">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245">
@@ -13559,6 +13659,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B245">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D245">
+        <is>
+          <t>Add Instrument UX incomplete (auto-close/validation)</t>
+        </is>
+      </c>
+      <c r="F245">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H245">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M245">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246">
@@ -13571,6 +13696,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B246">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D246">
+        <is>
+          <t>Table sorting not working</t>
+        </is>
+      </c>
+      <c r="F246">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H246">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M246">
+        <is>
+          <t>509d74d</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247">
@@ -13583,6 +13733,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B247">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D247">
+        <is>
+          <t>Watchlist columns insufficient</t>
+        </is>
+      </c>
+      <c r="F247">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H247">
+        <is>
+          <t>Artemis</t>
+        </is>
+      </c>
+      <c r="M247">
+        <is>
+          <t>230acdc</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248">
@@ -13595,6 +13770,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B248">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D248">
+        <is>
+          <t>Instrument search cannot reach backend</t>
+        </is>
+      </c>
+      <c r="F248">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H248">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="M248">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249">
@@ -13607,6 +13807,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B249">
+        <is>
+          <t>Shared Search</t>
+        </is>
+      </c>
+      <c r="D249">
+        <is>
+          <t>Multiple search implementations - unify service</t>
+        </is>
+      </c>
+      <c r="F249">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H249">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="M249">
+        <is>
+          <t/>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250">
@@ -13619,6 +13844,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B250">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D250">
+        <is>
+          <t>Key Metrics not rendering</t>
+        </is>
+      </c>
+      <c r="F250">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H250">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M250">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251">
@@ -13631,6 +13881,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B251">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D251">
+        <is>
+          <t>News feed empty</t>
+        </is>
+      </c>
+      <c r="F251">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H251">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M251">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252">
@@ -13643,6 +13918,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B252">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D252">
+        <is>
+          <t>Financials unavailable</t>
+        </is>
+      </c>
+      <c r="F252">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H252">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M252">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253">
@@ -13655,6 +13955,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B253">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D253">
+        <is>
+          <t>Financial labels overlap</t>
+        </is>
+      </c>
+      <c r="F253">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H253">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M253">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254">
@@ -13667,6 +13992,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B254">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D254">
+        <is>
+          <t>Analysis still contains mock content</t>
+        </is>
+      </c>
+      <c r="F254">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H254">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M254">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255">
@@ -13679,6 +14029,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B255">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D255">
+        <is>
+          <t>Options tab placeholder</t>
+        </is>
+      </c>
+      <c r="F255">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H255">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M255">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256">
@@ -13691,6 +14066,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B256">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D256">
+        <is>
+          <t>Chart symbol mismatch</t>
+        </is>
+      </c>
+      <c r="F256">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H256">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M256">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257">
@@ -13703,6 +14103,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B257">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D257">
+        <is>
+          <t>Analysis labels overlap</t>
+        </is>
+      </c>
+      <c r="F257">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H257">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M257">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258">
@@ -13715,6 +14140,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B258">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D258">
+        <is>
+          <t>Horizontal metrics carousel poor UX</t>
+        </is>
+      </c>
+      <c r="F258">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H258">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M258">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259">
@@ -13727,6 +14177,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B259">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D259">
+        <is>
+          <t>Three-dot menu inactive</t>
+        </is>
+      </c>
+      <c r="F259">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H259">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M259">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260">
@@ -13739,6 +14214,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B260">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D260">
+        <is>
+          <t>Customize Metrics uses old design</t>
+        </is>
+      </c>
+      <c r="F260">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H260">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M260">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261">
@@ -13751,6 +14251,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B261">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D261">
+        <is>
+          <t>Privacy control missing</t>
+        </is>
+      </c>
+      <c r="F261">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H261">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M261">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262">
@@ -13763,6 +14288,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B262">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D262">
+        <is>
+          <t>Recent News widget missing</t>
+        </is>
+      </c>
+      <c r="F262">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H262">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M262">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263">
@@ -13775,6 +14325,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B263">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D263">
+        <is>
+          <t>Targets should move to Overview</t>
+        </is>
+      </c>
+      <c r="F263">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H263">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M263">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264">
@@ -13787,6 +14362,31 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="B264">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D264">
+        <is>
+          <t>Analysis and Chart disconnected</t>
+        </is>
+      </c>
+      <c r="F264">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H264">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M264">
+        <is>
+          <t>62e6b3a</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265">
@@ -13797,6 +14397,31 @@
       <c r="G265">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+      <c r="B265">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D265">
+        <is>
+          <t>One-hand mobile handling improvements</t>
+        </is>
+      </c>
+      <c r="F265">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H265">
+        <is>
+          <t>Hermes</t>
+        </is>
+      </c>
+      <c r="M265">
+        <is>
+          <t>62e6b3a</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" ns1:id="rId1"/>
-    <sheet name="Backlog" sheetId="2" state="visible" ns1:id="rId2"/>
-    <sheet name="Roadmap" sheetId="3" state="visible" ns1:id="rId3"/>
-    <sheet name="Architecture Decisions" sheetId="4" state="visible" ns1:id="rId4"/>
-    <sheet name="UAT Log" sheetId="5" state="visible" ns1:id="rId5"/>
-    <sheet name="Approved Mocks" sheetId="6" state="visible" ns1:id="rId6"/>
-    <sheet name="Agent Tasks" sheetId="7" state="visible" ns1:id="rId7"/>
-    <sheet name="CURRENT_STATE" sheetId="8" state="visible" ns1:id="rId8"/>
-    <sheet name="UX_IMPROVEMENTS" sheetId="9" ns1:id="rId11"/>
-    <sheet name="CHANGELOG" sheetId="10" ns1:id="rId12"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Roadmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Architecture Decisions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="UAT Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Approved Mocks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Agent Tasks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CURRENT_STATE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UX_IMPROVEMENTS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CHANGELOG" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -279,14 +279,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
             <a:r>
               <a:rPr/>
               <a:t>Backlog by Status</a:t>
@@ -309,7 +309,7 @@
             <v>Count</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -352,7 +352,7 @@
         <axPos val="b"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -379,7 +379,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:ln w="9525">
               <a:solidFill>
                 <a:srgbClr val="CCCCCC"/>
               </a:solidFill>
@@ -403,7 +403,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+    <a:ln w="9525">
       <a:solidFill>
         <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
@@ -414,7 +414,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>10</col>
@@ -434,9 +434,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -685,1177 +685,1099 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:D69"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="14" customWidth="1" min="1" max="1"/>
-    <ns0:col width="28" customWidth="1" min="2" max="2"/>
-    <ns0:col width="72" customWidth="1" min="3" max="3"/>
-    <ns0:col width="10" customWidth="1" min="4" max="4"/>
-    <ns0:col width="18" customWidth="1" min="5" max="5"/>
-    <ns0:col width="18" customWidth="1" min="6" max="6"/>
-    <ns0:col width="28" customWidth="1" min="8" max="8"/>
-    <ns0:col width="10" customWidth="1" min="9" max="9"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="21" t="inlineStr">
-        <ns0:is>
-          <ns0:t>PIA Master Backlog Dashboard</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="n"/>
-      <ns0:c r="C1" s="1" t="n"/>
-      <ns0:c r="D1" s="1" t="n"/>
-      <ns0:c r="E1" s="1" t="n"/>
-      <ns0:c r="F1" s="1" t="n"/>
-      <ns0:c r="G1" s="1" t="n"/>
-      <ns0:c r="H1" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="25" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Generated: 2026-05-27 14:35 | Source of truth snapshot for project management</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="n"/>
-      <ns0:c r="C2" s="1" t="n"/>
-      <ns0:c r="D2" s="1" t="n"/>
-      <ns0:c r="E2" s="1" t="n"/>
-      <ns0:c r="F2" s="1" t="n"/>
-      <ns0:c r="G2" s="1" t="n"/>
-      <ns0:c r="H2" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="3"/>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Metric</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Value</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Notes</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Priority</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Category</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I4" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Items</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Total backlog items</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="12" t="n">
-        <ns0:v>215</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>All rows in Backlog sheet</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E5" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F5" t="n">
-        <ns0:v>42</ns0:v>
-      </ns0:c>
-      <ns0:c r="H5" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Academy</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I5" s="12" t="n">
-        <ns0:v>21</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0 items</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="12" t="n">
-        <ns0:v>42</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Critical / foundational</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F6" t="n">
-        <ns0:v>112</ns0:v>
-      </ns0:c>
-      <ns0:c r="H6" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Portfolio</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I6" s="12" t="n">
-        <ns0:v>18</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P1 items</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B7" s="12" t="n">
-        <ns0:v>112</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>High priority</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P2</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F7" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-      <ns0:c r="H7" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Earnings</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I7" s="12" t="n">
-        <ns0:v>13</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Done / Approved</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B8" s="12" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Delivered and approved</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H8" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Integrations</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I8" s="12" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Tech Pass / UAT pending</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B9" s="12" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Needs UAT</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H9" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Markets &amp; Macro</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I9" s="12" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Planned</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B10" s="12" t="n">
-        <ns0:v>148</ns0:v>
-      </ns0:c>
-      <ns0:c r="C10" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Future work</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H10" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Alerts</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I10" s="12" t="n">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="11">
-      <ns0:c r="A11" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>New bugs/items</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B11" s="12" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="C11" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Newly captured</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H11" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Backend</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I11" s="12" t="n">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="12">
-      <ns0:c r="E12" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Status</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F12" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Count</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H12" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I12" s="12" t="n">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="E13" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DONE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F13" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-      <ns0:c r="H13" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Notes</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I13" s="12" t="n">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" s="6" t="n"/>
-      <ns0:c r="B14" s="6" t="n"/>
-      <ns0:c r="C14" s="6" t="n"/>
-      <ns0:c r="D14" s="6" t="n"/>
-      <ns0:c r="E14" t="inlineStr">
-        <ns0:is>
-          <ns0:t>FOUNDATION DONE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F14" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="H14" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Workspace</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I14" s="12" t="n">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15">
-      <ns0:c r="A15" s="12" t="n"/>
-      <ns0:c r="B15" s="12" t="n"/>
-      <ns0:c r="C15" s="12" t="n"/>
-      <ns0:c r="D15" s="12" t="n"/>
-      <ns0:c r="E15" t="inlineStr">
-        <ns0:is>
-          <ns0:t>TECH PASS</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F15" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="H15" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Scanner</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I15" s="12" t="n">
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="16">
-      <ns0:c r="A16" s="12" t="n"/>
-      <ns0:c r="B16" s="12" t="n"/>
-      <ns0:c r="C16" s="12" t="n"/>
-      <ns0:c r="D16" s="12" t="n"/>
-      <ns0:c r="E16" t="inlineStr">
-        <ns0:is>
-          <ns0:t>IN PROGRESS</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F16" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="H16" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Backup</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I16" s="12" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="17">
-      <ns0:c r="A17" s="12" t="n"/>
-      <ns0:c r="B17" s="12" t="n"/>
-      <ns0:c r="C17" s="12" t="n"/>
-      <ns0:c r="D17" s="12" t="n"/>
-      <ns0:c r="E17" t="inlineStr">
-        <ns0:is>
-          <ns0:t>NEW</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F17" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="H17" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Command</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I17" s="12" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="18">
-      <ns0:c r="A18" s="12" t="n"/>
-      <ns0:c r="B18" s="12" t="n"/>
-      <ns0:c r="C18" s="12" t="n"/>
-      <ns0:c r="D18" s="12" t="n"/>
-      <ns0:c r="E18" t="inlineStr">
-        <ns0:is>
-          <ns0:t>PLANNED</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F18" t="n">
-        <ns0:v>148</ns0:v>
-      </ns0:c>
-      <ns0:c r="H18" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Performance</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I18" s="12" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="19">
-      <ns0:c r="A19" s="12" t="n"/>
-      <ns0:c r="B19" s="12" t="n"/>
-      <ns0:c r="C19" s="12" t="n"/>
-      <ns0:c r="D19" s="12" t="n"/>
-      <ns0:c r="E19" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ENVIRONMENT</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F19" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="H19" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Settings</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I19" s="12" t="n">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="20">
-      <ns0:c r="H20" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>AI Core</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I20" s="12" t="n">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="21">
-      <ns0:c r="H21" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>AI Infrastructure</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I21" s="12" t="n">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="22">
-      <ns0:c r="A22" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>When</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B22" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Action</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C22" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Description</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D22" s="6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Priority</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H22" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Crypto</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I22" s="12" t="n">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="23">
-      <ns0:c r="A23" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Now</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B23" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Sprint 2B Mock Compliance</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C23" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Athena: mobile-first Home mock compliance; Hermes: stock/news/videos mock compliance.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D23" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H23" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Discord</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I23" s="12" t="n">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="24">
-      <ns0:c r="A24" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Next</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B24" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UAT after preview/local</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C24" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UAT must be mock-compliance, not only load/no crash.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D24" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H24" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Trade Coach</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I24" s="12" t="n">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="25">
-      <ns0:c r="A25" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DONE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B25" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Backlog/Git file update</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C25" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Commit XLSX + markdown/JSON source-of-truth into repo.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D25" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H25" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Watchlists</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I25" s="12" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="26">
-      <ns0:c r="A26" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Later</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B26" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Vercel mobile preview</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C26" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Branch preview URLs for mobile UAT.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D26" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H26" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Bug</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I26" s="12" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="27">
-      <ns0:c r="A27" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Later</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B27" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Portfolio V3 MVP</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C27" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>My Portfolio with snapshots, heatmap, attribution, targets, intelligence.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D27" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H27" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Voice</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I27" s="12" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="28">
-      <ns0:c r="A28" s="12" t="n"/>
-      <ns0:c r="B28" s="12" t="n"/>
-      <ns0:c r="H28" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Foundation</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I28" s="12" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="29">
-      <ns0:c r="A29" s="12" t="n"/>
-      <ns0:c r="B29" s="12" t="n"/>
-      <ns0:c r="H29" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Sources</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I29" s="12" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="30">
-      <ns0:c r="A30" s="12" t="n"/>
-      <ns0:c r="B30" s="12" t="n"/>
-      <ns0:c r="H30" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>DevOps</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I30" s="12" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="31">
-      <ns0:c r="A31" s="12" t="n"/>
-      <ns0:c r="B31" s="12" t="n"/>
-      <ns0:c r="H31" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Stock Workspace</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I31" s="12" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="32">
-      <ns0:c r="A32" s="12" t="n"/>
-      <ns0:c r="B32" s="12" t="n"/>
-      <ns0:c r="H32" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Change</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I32" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="33">
-      <ns0:c r="A33" s="12" t="n"/>
-      <ns0:c r="B33" s="12" t="n"/>
-      <ns0:c r="H33" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Design System</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I33" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="34">
-      <ns0:c r="A34" s="12" t="n"/>
-      <ns0:c r="B34" s="12" t="n"/>
-      <ns0:c r="H34" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Heatmap</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I34" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="35">
-      <ns0:c r="A35" s="12" t="n"/>
-      <ns0:c r="B35" s="12" t="n"/>
-      <ns0:c r="H35" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>News</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I35" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="36">
-      <ns0:c r="A36" s="12" t="n"/>
-      <ns0:c r="B36" s="12" t="n"/>
-      <ns0:c r="H36" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Process</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I36" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="37">
-      <ns0:c r="A37" s="12" t="n"/>
-      <ns0:c r="B37" s="12" t="n"/>
-      <ns0:c r="H37" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Stock Intelligence</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I37" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="38">
-      <ns0:c r="A38" s="12" t="n"/>
-      <ns0:c r="B38" s="12" t="n"/>
-      <ns0:c r="H38" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UI/UX</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I38" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="39">
-      <ns0:c r="A39" s="12" t="n"/>
-      <ns0:c r="B39" s="12" t="n"/>
-      <ns0:c r="H39" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>UX</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I39" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="40">
-      <ns0:c r="A40" s="12" t="n"/>
-      <ns0:c r="B40" s="12" t="n"/>
-      <ns0:c r="H40" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Widgets</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I40" s="12" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="41">
-      <ns0:c r="A41" s="12" t="n"/>
-      <ns0:c r="B41" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="42">
-      <ns0:c r="A42" s="12" t="n"/>
-      <ns0:c r="B42" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="43">
-      <ns0:c r="A43" s="12" t="n"/>
-      <ns0:c r="B43" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="44">
-      <ns0:c r="A44" s="12" t="n"/>
-      <ns0:c r="B44" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="45">
-      <ns0:c r="A45" s="12" t="n"/>
-      <ns0:c r="B45" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="46">
-      <ns0:c r="A46" s="12" t="n"/>
-      <ns0:c r="B46" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="47">
-      <ns0:c r="A47" s="12" t="n"/>
-      <ns0:c r="B47" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="48">
-      <ns0:c r="A48" s="12" t="n"/>
-      <ns0:c r="B48" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="49">
-      <ns0:c r="A49" s="12" t="n"/>
-      <ns0:c r="B49" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="50">
-      <ns0:c r="A50" s="12" t="n"/>
-      <ns0:c r="B50" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="51">
-      <ns0:c r="A51" s="12" t="n"/>
-      <ns0:c r="B51" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="52">
-      <ns0:c r="A52" s="12" t="n"/>
-      <ns0:c r="B52" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="53">
-      <ns0:c r="A53" s="12" t="n"/>
-      <ns0:c r="B53" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="54">
-      <ns0:c r="A54" s="12" t="n"/>
-      <ns0:c r="B54" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="55">
-      <ns0:c r="A55" s="12" t="n"/>
-      <ns0:c r="B55" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="56">
-      <ns0:c r="A56" s="12" t="n"/>
-      <ns0:c r="B56" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="57">
-      <ns0:c r="A57" s="12" t="n"/>
-      <ns0:c r="B57" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="58">
-      <ns0:c r="A58" s="12" t="n"/>
-      <ns0:c r="B58" s="12" t="n"/>
-    </ns0:row>
-    <ns0:row r="59">
-      <ns0:c r="A59" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Route</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B59" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Purpose</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C59" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Validation Expectation</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="60">
-      <ns0:c r="A60" t="inlineStr">
-        <ns0:is>
-          <ns0:t>/</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B60" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Home dashboard and desktop workspace shell</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C60" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Must load with no route regression; widgets must be clickable</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="61">
-      <ns0:c r="A61" t="inlineStr">
-        <ns0:is>
-          <ns0:t>/mobile</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B61" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile-first command experience</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C61" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Polished, compact, readable, no horizontal overflow; swipe must work</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="62">
-      <ns0:c r="A62" t="inlineStr">
-        <ns0:is>
-          <ns0:t>/setup</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B62" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Setup and onboarding flow</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C62" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Must remain preserved</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="63">
-      <ns0:c r="A63" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Priority</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B63" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Area</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C63" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Requirement</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="64">
-      <ns0:c r="A64" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B64" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Home dashboard</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C64" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Premium visual identity while preserving working widgets</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="65">
-      <ns0:c r="A65" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B65" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile Home</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C65" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Must not feel like squeezed desktop</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="66">
-      <ns0:c r="A66" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B66" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Privacy mode</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C66" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Amount hiding must remain intact</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="67">
-      <ns0:c r="A67" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P0</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B67" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Notifications</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C67" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile-safe Notification Center with grouped premium cards</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="68">
-      <ns0:c r="A68" t="inlineStr">
-        <ns0:is>
-          <ns0:t>P1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B68" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Status dock</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C68" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="69">
-      <ns0:c r="A69" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>v0.3.15</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B69" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Workspace Manager + Custom Workspaces</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C69" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Implemented 2026-05-28</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D69" s="12" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Mobile hamburger manager, direct overflow workspace open, Settings/About access, configurable pinned bottom nav, desktop sidebar parity, custom local workspaces.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:mergeCells count="2">
-    <ns0:mergeCell ref="A2:H2"/>
-    <ns0:mergeCell ref="A1:H1"/>
-  </ns0:mergeCells>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ns0:drawing ns1:id="rId1"/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>PIA Master Backlog Dashboard</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Generated: 2026-05-27 14:35 | Source of truth snapshot for project management</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Total backlog items</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>All rows in Backlog sheet</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>42</v>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Academy</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>P0 items</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Critical / foundational</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>112</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>P1 items</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>High priority</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Done / Approved</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Delivered and approved</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>Integrations</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Tech Pass / UAT pending</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Needs UAT</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Markets &amp; Macro</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Future work</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>New bugs/items</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Newly captured</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FOUNDATION DONE</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>Workspace</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TECH PASS</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Scanner</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n"/>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>148</v>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n"/>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>AI Core</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 2B Mock Compliance</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Athena: mobile-first Home mock compliance; Hermes: stock/news/videos mock compliance.</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Discord</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Next</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>UAT after preview/local</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>UAT must be mock-compliance, not only load/no crash.</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>Trade Coach</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Backlog/Git file update</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Commit XLSX + markdown/JSON source-of-truth into repo.</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Vercel mobile preview</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Branch preview URLs for mobile UAT.</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio V3 MVP</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>My Portfolio with snapshots, heatmap, attribution, targets, intelligence.</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>Foundation</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>Stock Workspace</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Design System</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>Heatmap</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="n"/>
+      <c r="B36" s="12" t="n"/>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="n"/>
+      <c r="B37" s="12" t="n"/>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="n"/>
+      <c r="B38" s="12" t="n"/>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n"/>
+      <c r="B39" s="12" t="n"/>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n"/>
+      <c r="B40" s="12" t="n"/>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>Widgets</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="n"/>
+      <c r="B41" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n"/>
+      <c r="B42" s="12" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n"/>
+      <c r="B43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n"/>
+      <c r="B44" s="12" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="n"/>
+      <c r="B45" s="12" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n"/>
+      <c r="B46" s="12" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n"/>
+      <c r="B47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n"/>
+      <c r="B48" s="12" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="n"/>
+      <c r="B49" s="12" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n"/>
+      <c r="B50" s="12" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n"/>
+      <c r="B51" s="12" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="n"/>
+      <c r="B52" s="12" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="n"/>
+      <c r="B53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="n"/>
+      <c r="B54" s="12" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="n"/>
+      <c r="B55" s="12" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="n"/>
+      <c r="B56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="n"/>
+      <c r="B57" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="n"/>
+      <c r="B58" s="12" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Validation Expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Home dashboard and desktop workspace shell</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Must load with no route regression; widgets must be clickable</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>/mobile</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mobile-first command experience</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Polished, compact, readable, no horizontal overflow; swipe must work</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>/setup</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Setup and onboarding flow</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Must remain preserved</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Home dashboard</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Premium visual identity while preserving working widgets</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Mobile Home</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Must not feel like squeezed desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Privacy mode</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Amount hiding must remain intact</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Mobile-safe Notification Center with grouped premium cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Status dock</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Surface IBKR, Yahoo, and Feeds status in compact shell UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>v0.3.15</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Workspace Manager + Custom Workspaces</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Implemented 2026-05-28</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Mobile hamburger manager, direct overflow workspace open, Settings/About access, configurable pinned bottom nav, desktop sidebar parity, custom local workspaces.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1">
-        <is>
-          <t>Commit</t>
-        </is>
-      </c>
-      <c r="C1">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-      <c r="D1">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B2">
-        <is>
-          <t>230acdc</t>
-        </is>
-      </c>
-      <c r="C2">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="D2">
-        <is>
-          <t>Watchlist unified column manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B3">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-      <c r="C3">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="D3">
-        <is>
-          <t>Watchlists Mobile V1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B4">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-      <c r="C4">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="D4">
-        <is>
-          <t>Stock Intelligence data recovery attempt</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M265"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2594,7 +2516,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>PIA-BUG-027</t>
@@ -13366,7 +13288,7 @@
         </is>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
           <t>PIA-UX-032</t>
@@ -13433,7 +13355,7 @@
         </is>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
           <t>PIA-UX-033</t>
@@ -13500,928 +13422,95 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241">
-        <is>
-          <t>PIA-WL-008</t>
-        </is>
-      </c>
-      <c r="G241">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B241">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D241">
-        <is>
-          <t>Manage Columns uses buttons instead of switches</t>
-        </is>
-      </c>
-      <c r="F241">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H241">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M241">
-        <is>
-          <t>230acdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242">
-        <is>
-          <t>PIA-WL-009</t>
-        </is>
-      </c>
-      <c r="G242">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B242">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D242">
-        <is>
-          <t>Open Chart opens wrong destination</t>
-        </is>
-      </c>
-      <c r="F242">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H242">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M242">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243">
-        <is>
-          <t>PIA-WL-010</t>
-        </is>
-      </c>
-      <c r="G243">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B243">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D243">
-        <is>
-          <t>Add To Watchlist does nothing (lists not shown)</t>
-        </is>
-      </c>
-      <c r="F243">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H243">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M243">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244">
-        <is>
-          <t>PIA-WL-011</t>
-        </is>
-      </c>
-      <c r="G244">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B244">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D244">
-        <is>
-          <t>AI Coach inactive</t>
-        </is>
-      </c>
-      <c r="F244">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H244">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M244">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245">
-        <is>
-          <t>PIA-WL-012</t>
-        </is>
-      </c>
-      <c r="G245">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B245">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D245">
-        <is>
-          <t>Add Instrument UX incomplete (auto-close/validation)</t>
-        </is>
-      </c>
-      <c r="F245">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H245">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M245">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246">
-        <is>
-          <t>PIA-WL-013</t>
-        </is>
-      </c>
-      <c r="G246">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B246">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D246">
-        <is>
-          <t>Table sorting not working</t>
-        </is>
-      </c>
-      <c r="F246">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H246">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M246">
-        <is>
-          <t>509d74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247">
-        <is>
-          <t>PIA-WL-014</t>
-        </is>
-      </c>
-      <c r="G247">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B247">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D247">
-        <is>
-          <t>Watchlist columns insufficient</t>
-        </is>
-      </c>
-      <c r="F247">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H247">
-        <is>
-          <t>Artemis</t>
-        </is>
-      </c>
-      <c r="M247">
-        <is>
-          <t>230acdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248">
-        <is>
-          <t>PIA-SHARED-001</t>
-        </is>
-      </c>
-      <c r="G248">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B248">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D248">
-        <is>
-          <t>Instrument search cannot reach backend</t>
-        </is>
-      </c>
-      <c r="F248">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H248">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="M248">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249">
-        <is>
-          <t>PIA-SHARED-002</t>
-        </is>
-      </c>
-      <c r="G249">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B249">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D249">
-        <is>
-          <t>Multiple search implementations - unify service</t>
-        </is>
-      </c>
-      <c r="F249">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H249">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="M249">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250">
-        <is>
-          <t>PIA-SI-001</t>
-        </is>
-      </c>
-      <c r="G250">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B250">
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CR-AT-003/004/005-BUG-AT-001</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
         <is>
           <t>Stock Intelligence</t>
         </is>
       </c>
-      <c r="D250">
-        <is>
-          <t>Key Metrics not rendering</t>
-        </is>
-      </c>
-      <c r="F250">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H250">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M250">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251">
-        <is>
-          <t>PIA-SI-002</t>
-        </is>
-      </c>
-      <c r="G251">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B251">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D251">
-        <is>
-          <t>News feed empty</t>
-        </is>
-      </c>
-      <c r="F251">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H251">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M251">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252">
-        <is>
-          <t>PIA-SI-003</t>
-        </is>
-      </c>
-      <c r="G252">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B252">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D252">
-        <is>
-          <t>Financials unavailable</t>
-        </is>
-      </c>
-      <c r="F252">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H252">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M252">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253">
-        <is>
-          <t>PIA-SI-004</t>
-        </is>
-      </c>
-      <c r="G253">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B253">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D253">
-        <is>
-          <t>Financial labels overlap</t>
-        </is>
-      </c>
-      <c r="F253">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H253">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M253">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254">
-        <is>
-          <t>PIA-SI-005</t>
-        </is>
-      </c>
-      <c r="G254">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B254">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D254">
-        <is>
-          <t>Analysis still contains mock content</t>
-        </is>
-      </c>
-      <c r="F254">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H254">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M254">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255">
-        <is>
-          <t>PIA-SI-006</t>
-        </is>
-      </c>
-      <c r="G255">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B255">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D255">
-        <is>
-          <t>Options tab placeholder</t>
-        </is>
-      </c>
-      <c r="F255">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H255">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M255">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256">
-        <is>
-          <t>PIA-SI-007</t>
-        </is>
-      </c>
-      <c r="G256">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B256">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D256">
-        <is>
-          <t>Chart symbol mismatch</t>
-        </is>
-      </c>
-      <c r="F256">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="H256">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M256">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257">
-        <is>
-          <t>PIA-SI-008</t>
-        </is>
-      </c>
-      <c r="G257">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B257">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D257">
-        <is>
-          <t>Analysis labels overlap</t>
-        </is>
-      </c>
-      <c r="F257">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H257">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M257">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258">
-        <is>
-          <t>PIA-SI-009</t>
-        </is>
-      </c>
-      <c r="G258">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B258">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D258">
-        <is>
-          <t>Horizontal metrics carousel poor UX</t>
-        </is>
-      </c>
-      <c r="F258">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H258">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M258">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259">
-        <is>
-          <t>PIA-SI-010</t>
-        </is>
-      </c>
-      <c r="G259">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B259">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D259">
-        <is>
-          <t>Three-dot menu inactive</t>
-        </is>
-      </c>
-      <c r="F259">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H259">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M259">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260">
-        <is>
-          <t>PIA-SI-011</t>
-        </is>
-      </c>
-      <c r="G260">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B260">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D260">
-        <is>
-          <t>Customize Metrics uses old design</t>
-        </is>
-      </c>
-      <c r="F260">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H260">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M260">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261">
-        <is>
-          <t>PIA-SI-012</t>
-        </is>
-      </c>
-      <c r="G261">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B261">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D261">
-        <is>
-          <t>Privacy control missing</t>
-        </is>
-      </c>
-      <c r="F261">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H261">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M261">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262">
-        <is>
-          <t>PIA-SI-013</t>
-        </is>
-      </c>
-      <c r="G262">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B262">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D262">
-        <is>
-          <t>Recent News widget missing</t>
-        </is>
-      </c>
-      <c r="F262">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H262">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M262">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263">
-        <is>
-          <t>PIA-SI-014</t>
-        </is>
-      </c>
-      <c r="G263">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B263">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D263">
-        <is>
-          <t>Targets should move to Overview</t>
-        </is>
-      </c>
-      <c r="F263">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H263">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M263">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264">
-        <is>
-          <t>PIA-SI-015</t>
-        </is>
-      </c>
-      <c r="G264">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B264">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D264">
-        <is>
-          <t>Analysis and Chart disconnected</t>
-        </is>
-      </c>
-      <c r="F264">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H264">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M264">
-        <is>
-          <t>62e6b3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265">
-        <is>
-          <t>PIA-SI-016</t>
-        </is>
-      </c>
-      <c r="G265">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="B265">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D265">
-        <is>
-          <t>One-hand mobile handling improvements</t>
-        </is>
-      </c>
-      <c r="F265">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H265">
-        <is>
-          <t>Hermes</t>
-        </is>
-      </c>
-      <c r="M265">
-        <is>
-          <t>62e6b3a</t>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Analyst Targets V2</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Analyst Targets usability and detail view</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Prominent IBKR-style upside/downside badge with dollar delta; Overview card opens Analysis; Analysis tab includes consensus/bull/bear targets, recommendation summary, analyst count, and analyst history empty state.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration / latest HERMES Analyst Targets V2 commit</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>READY FOR UAT</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Yahoo fallback supports consensus/recommendation summary; firm/date previous-target/new-target history requires Finnhub/FMP or another provider.</t>
         </is>
       </c>
     </row>
@@ -14458,13 +13547,13 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart ns1:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -15097,13 +14186,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -15849,18 +14938,18 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16742,791 +15831,98 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C23">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D23">
-        <is>
-          <t>Long press Open Chart opens wrong destination</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C24">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D24">
-        <is>
-          <t>Add To Watchlist non-functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C25">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D25">
-        <is>
-          <t>AI Coach non-functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C26">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D26">
-        <is>
-          <t>Add Instrument stays permanently open</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C27">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D27">
-        <is>
-          <t>Table sorting not working</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C28">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D28">
-        <is>
-          <t>Column catalog limited</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C29">
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>UAT-AT-V2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Stock Intelligence</t>
         </is>
       </c>
-      <c r="D29">
-        <is>
-          <t>Key metrics N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C30">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D30">
-        <is>
-          <t>Today Range missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C31">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D31">
-        <is>
-          <t>News empty</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C32">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D32">
-        <is>
-          <t>Financials unavailable</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C33">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D33">
-        <is>
-          <t>Analysis placeholders</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C34">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D34">
-        <is>
-          <t>Analysis label overlap</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C35">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D35">
-        <is>
-          <t>Financial label overlap</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C36">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D36">
-        <is>
-          <t>Options tab placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C37">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D37">
-        <is>
-          <t>Three-dot menu inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C38">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D38">
-        <is>
-          <t>Privacy action missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C39">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D39">
-        <is>
-          <t>Targets not in Overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C40">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D40">
-        <is>
-          <t>Chart/Analysis disconnected</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C41">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D41">
-        <is>
-          <t>Manual Holdings search reports backend unavailable</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C42">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D42">
-        <is>
-          <t>Watchlist search affected</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C43">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D43">
-        <is>
-          <t>Search icon affected</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C44">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D44">
-        <is>
-          <t>Long Press → Open Chart opens wrong destination</t>
-        </is>
-      </c>
-      <c r="H44">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C45">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D45">
-        <is>
-          <t>Add To Watchlist does not show available lists</t>
-        </is>
-      </c>
-      <c r="H45">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C46">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D46">
-        <is>
-          <t>AI Coach does not perform actions</t>
-        </is>
-      </c>
-      <c r="H46">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C47">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D47">
-        <is>
-          <t>Add ticker field stays permanently open</t>
-        </is>
-      </c>
-      <c r="H47">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C48">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D48">
-        <is>
-          <t>Table sorting (LAST/CHNG/CHG%/VLM) not working</t>
-        </is>
-      </c>
-      <c r="H48">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C49">
-        <is>
-          <t>Watchlists</t>
-        </is>
-      </c>
-      <c r="D49">
-        <is>
-          <t>Watchlist columns insufficient (missing financial metrics)</t>
-        </is>
-      </c>
-      <c r="H49">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C50">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D50">
-        <is>
-          <t>News tab empty for NVDA</t>
-        </is>
-      </c>
-      <c r="H50">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C51">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D51">
-        <is>
-          <t>Estimate vs Actual overlaps Earnings</t>
-        </is>
-      </c>
-      <c r="H51">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C52">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D52">
-        <is>
-          <t>Analysis labels overlap on mobile</t>
-        </is>
-      </c>
-      <c r="H52">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C53">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D53">
-        <is>
-          <t>Key Metrics show N/A (Open/DayHigh/DayLow/Volume/AvgVolume)</t>
-        </is>
-      </c>
-      <c r="H53">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C54">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D54">
-        <is>
-          <t>Financial sections unavailable</t>
-        </is>
-      </c>
-      <c r="H54">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C55">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D55">
-        <is>
-          <t>Analysis still contains mock content</t>
-        </is>
-      </c>
-      <c r="H55">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C56">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D56">
-        <is>
-          <t>Options tab placeholder should be removed</t>
-        </is>
-      </c>
-      <c r="H56">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C57">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D57">
-        <is>
-          <t>Three-dot menu (⋮) inactive</t>
-        </is>
-      </c>
-      <c r="H57">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C58">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D58">
-        <is>
-          <t>Privacy toggle missing from UI</t>
-        </is>
-      </c>
-      <c r="H58">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C59">
-        <is>
-          <t>Stock Intelligence</t>
-        </is>
-      </c>
-      <c r="D59">
-        <is>
-          <t>Targets not shown in Overview</t>
-        </is>
-      </c>
-      <c r="H59">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C60">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D60">
-        <is>
-          <t>Manual Holdings: Instrument search reports backend unreachable</t>
-        </is>
-      </c>
-      <c r="H60">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C61">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D61">
-        <is>
-          <t>Watchlist Add Instrument search affected</t>
-        </is>
-      </c>
-      <c r="H61">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="C62">
-        <is>
-          <t>Shared Search</t>
-        </is>
-      </c>
-      <c r="D62">
-        <is>
-          <t>Search icon/ticker search failing</t>
-        </is>
-      </c>
-      <c r="H62">
-        <is>
-          <t/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Analyst Targets V2 Overview and Analysis detail behavior for NVDA/AMD/MSFT/SOFI</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Card before News, prominent percent and dollar delta, tap opens Analysis, detail section present, unavailable history state shown without fake rows.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>TECH PASS</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>READY FOR PO UAT</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Build/routes passed locally. Yahoo payload has consensus/recommendation data; analyst history rows unavailable in fallback provider.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart ns1:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17943,18 +16339,18 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18714,10 +17110,52 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TASK-HERMES-AT-V2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Analyst Targets V2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Overview badge prominence, tap-to-Analysis, Analysis detail and history empty state, provider recommendation summary preservation.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED - latest HERMES Analyst Targets V2 commit</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>npm run build; route smoke / /mobile /setup; UAT tickers NVDA AMD MSFT SOFI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PO UAT; choose Finnhub/FMP for firm-level target history if required.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -18775,7 +17213,7 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Sprint 2C</t>
+          <t>Analyst Targets V2 validation / Mobile UAT</t>
         </is>
       </c>
     </row>
@@ -19031,7 +17469,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>Release Reference</t>
@@ -19050,103 +17488,22 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <is>
-          <t>UX-001</t>
-        </is>
-      </c>
-      <c r="B2">
-        <is>
-          <t>Move analyst targets into Overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <is>
-          <t>UX-002</t>
-        </is>
-      </c>
-      <c r="B3">
-        <is>
-          <t>Remove Options tab until functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <is>
-          <t>UX-003</t>
-        </is>
-      </c>
-      <c r="B4">
-        <is>
-          <t>Replace ON/OFF buttons with mobile switches</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <is>
-          <t>UX-004</t>
-        </is>
-      </c>
-      <c r="B5">
-        <is>
-          <t>Auto-close Add Instrument after success</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <is>
-          <t>UX-005</t>
-        </is>
-      </c>
-      <c r="B6">
-        <is>
-          <t>Source + relative time on news</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <is>
-          <t>UX-006</t>
-        </is>
-      </c>
-      <c r="B7">
-        <is>
-          <t>One-hand mobile interaction improvements</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <is>
-          <t>UX-007</t>
-        </is>
-      </c>
-      <c r="B8">
-        <is>
-          <t>Unify Customize Metrics with Manage Columns pattern</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,13 +1759,449 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>02dfcdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>move market session line to portfolio header</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0778807</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HERMES/ATHENA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>portfolio and hero ux polish</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>b7c646f</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>portfolio grid and filters sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0e36100</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>move today range into stock hero</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6038934</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>improve live price emphasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>54bf30e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>add portfolio card customization framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>68c0656</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>compact stock hero range and sparkline layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23bce57</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>portfolio and watchlist cards v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>44d7fb1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>add analyst price targets widget</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2948a0f</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>refine analyst targets placement and detail view</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>edca406</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>polish portfolio watchlist visual system</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>803e929</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>enhance analyst targets detail view</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5e8daca</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UAT CR-PC-001 2x2 card compact IBKR style</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2b9d1de</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>implement analyst targets v3 layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5602655</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>prioritize analyst target upside badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ecbe06d</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>refine analyst targets navigation and density</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ac0ca6f</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>compact analyst target percentages</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>72499e9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>UAT fix pack: empty widgets, logo ring, portfolio view selector</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>e5736e9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mobile density pass + persistence validation + view selector polish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1777,7 +2213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M266"/>
+  <dimension ref="A1:M272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13511,6 +13947,360 @@
       <c r="M266" t="inlineStr">
         <is>
           <t>Yahoo fallback supports consensus/recommendation summary; firm/date previous-target/new-target history requires Finnhub/FMP or another provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CR-AT-V3</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Analyst Targets V3</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>V3 layout: Options tab removed; chart only in Chart tab; fixed sticky header; Overview Bull/Base/Bear + target range + consensus + analyst distribution; Analysis subsection (Consensus, Bull/Base/Bear, Distribution, History cards)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Tap Overview card navigates to Analysis &gt; Analyst Targets; history as mobile cards (no tables)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>READY FOR UAT</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Commits 2b9d1de,5602655,ecbe06d,ac0ca6f through e5736e9; current data source only (no Finnhub/FMP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SPRINT-PORT-DENSITY</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Portfolio / Cards</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Portfolio Density Sprint</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Cards v2; card customization framework; grid + filters; 2x2 compact IBKR; live price emphasis (color/pop); visual system v2 (logo/hierarchy/2x2); logo ring; portfolio view selector; mobile density pass + persistence validation</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Portfolio &amp; Watchlist card visual system</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>READY FOR UAT</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Commits 23bce57,54bf30e,b7c646f,6038934,edca406,5e8daca,72499e9,e5736e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>PIA-UX-060</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Portfolio / Watchlist</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Card Visuals</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Card logo still under-weighted as visual anchor</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Logo competes with price/ticker; push size/contrast</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Visual audit 2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>PIA-BUG-032</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Workspaces</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Live Widgets</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Empty workspace preview widgets read as broken-premium</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Faded placeholder panels on Portfolio/Watchlist pages</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>ATHENA / Platform</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Visual audit 2026-06-09; ties to live-widget conversion</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>PIA-CSS-001</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Duplicated/overriding .stock-intel-header CSS; consolidate before V3 fixed header</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>h2/price/symbol-mark declared multiple times in globals.css</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Visual audit 2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PIA-UX-061</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>View Mode</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Cards view discoverability: view mode buried in overflow menu</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Consider visible 1x1/2x2/3x3 segmented control</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>PO decision</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Visual audit 2026-06-09</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14932,6 +15722,60 @@
       <c r="E29" s="12" t="inlineStr">
         <is>
           <t>No widget, screen, workspace, navigation change, or major refactor may be implemented before mock creation, PO review, corrections, APPROVED status, and storage in docs/design-system/mocks/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DEC-DESIGN-LOCK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Process Governance</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Design Lock: a feature marked DESIGN LOCKED has its layout/IA frozen; implementation must match the locked spec; deviations require re-approval</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Introduced with the Analyst Targets V3 design-locked spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DEC-NEXT-CACHE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Build Governance</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Next.js cache rule: on PageNotFoundError during page-data collection (/_not-found, /_document), clear .next then rebuild; never delete .next while a dev/prod server holds it (file lock); avoid concurrent .next access in the shared working tree</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recurring build contention during 2026-06 multi-agent sprints</t>
         </is>
       </c>
     </row>
@@ -14949,7 +15793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15913,6 +16757,258 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UAT-AT-V3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Analyst Targets V3 Overview + Analysis</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Options removed; chart only in Chart tab; Overview bull/base/bear + range + consensus + distribution; tap to Analysis history cards</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>TECH PASS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>READY FOR PO UAT</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Current data source; firm-level history limited without Finnhub/FMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UAT-PORT-DENSITY</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Portfolio / Watchlist</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Card density, logo, price emphasis, view selector, 2x2/3x3</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Build passed; / /mobile /setup 200; cards render across 1x1/2x2/3x3</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>TECH PASS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>READY FOR PO UAT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Screenshots captured desktop 1440 + mobile 390</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UAT-VIS-001</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Portfolio / Watchlist</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Visual audit: logo sizing</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Logo a strong anchor</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>FINDING</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Logo still small vs price/ticker (PIA-UX-060)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UAT-VIS-002</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Workspaces</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Visual audit: empty preview widgets</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Premium-feeling cards</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>FINDING</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Empty workspace preview panels look broken-premium (PIA-BUG-032)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UAT-VIS-003</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Visual audit: stock header CSS</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Single consistent header</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>FINDING</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Duplicated .stock-intel-header rules (PIA-CSS-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UAT-WL-CARRY</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Watchlists</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Carry-forward watchlist UAT (PIA-WL-008..014)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Column switches; Open Chart target; Add-to-list; AI Coach; add-instrument UX; sorting; columns</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Carried from 2026-06-02 watchlist UAT; still open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -17492,18 +18588,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,6 +2199,28 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>mobile density pass + persistence validation + view selector polish</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AI-V2-LOCK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2 Design Lock: KPI cards, single bottom-sheet explainability, no-collapse policy approved; DEC-AI-001/002/003 LOCKED; CR-AI-010 READY; V1 deprecated</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M272"/>
+  <dimension ref="A1:M273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14130,9 +14152,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-      <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
           <t>Visual audit 2026-06-09</t>
@@ -14185,9 +14204,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
           <t>Visual audit 2026-06-09; ties to live-widget conversion</t>
@@ -14240,9 +14256,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
           <t>Visual audit 2026-06-09</t>
@@ -14295,12 +14308,76 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
           <t>Visual audit 2026-06-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CR-AI-010</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2 implementation: KPI cards, single bottom-sheet explainability, no-collapse policy, score vs directional KPI families</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Implements DEC-AI-001/002/003; V1 deprecated</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>READY FOR IMPLEMENTATION</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>DESIGN LOCKED</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Spec: docs/design-system/mocks/stock-workspace/ai-intelligence-widget-v2.md; design score 10/10; PO approved</t>
         </is>
       </c>
     </row>
@@ -14987,7 +15064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15776,6 +15853,87 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>Recurring build contention during 2026-06 multi-agent sprints</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DEC-AI-001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KPI Cards: replace KPI rings with KPI cards (Value, Trend Delta, Label, Status, Chevron); full-card tap target; no ring gauges; no flat statistic tiles. Score family (Momentum/Trend/Sentiment, 0-100) vs Directional family (Institutional Flow, Price vs Fair Value) must be visually distinct.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Better information density, mobile usability, larger tap targets, improved explainability (AI Intelligence V2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DEC-AI-002</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Single Bottom Sheet Explainability: tap KPI opens one scrollable bottom sheet with Why It Matters -&gt; Score Breakdown -&gt; Historical Evolution -&gt; Disclaimer. No nested drilldowns, no multiple screens, no modal chains.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Institutional-grade explainability kept one-hand mobile (AI Intelligence V2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DEC-AI-003</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>No Widget Collapse on missing data: render the full widget structure and show missing values as "--"; forbidden to replace the section with "Data gathering in progress". Maintain layout stability.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Layout stability and premium feel with thin data payloads (AI Intelligence V2)</t>
         </is>
       </c>
     </row>
@@ -16675,46 +16833,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2221,6 +2221,28 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>AI Intelligence V2 Design Lock: KPI cards, single bottom-sheet explainability, no-collapse policy approved; DEC-AI-001/002/003 LOCKED; CR-AI-010 READY; V1 deprecated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GOV-004</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PIA-GOV-004 Approved Mock Preservation &amp; Design Lock Traceability LOCKED (DEC-GOV-004); compliance audit + GOV-004-REMEDIATION created</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M273"/>
+  <dimension ref="A1:M274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14378,6 +14400,61 @@
       <c r="M273" t="inlineStr">
         <is>
           <t>Spec: docs/design-system/mocks/stock-workspace/ai-intelligence-widget-v2.md; design score 10/10; PO approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>GOV-004-REMEDIATION</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Approved Mock Compliance</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Normalize existing approved mocks to APPROVED_&lt;feature&gt;_v&lt;version&gt;.png; consolidate docs/mocks vs docs/design-system/mocks; resolve "AI Intelligence/mock v1.png" vs locked AI Intelligence V2 version; backfill traceability triples (Approved Mock / Design Lock Commit / Implementation Commit).</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Non-compliant assets: docs/mocks/AI Intelligence/mock v1.png; docs/mocks/analyst-targets/Approved_mobile_mock_analyst_target.jpg; docs/mocks/stock-intelligence/stock-intelligence-v1-approved.png; docs/mocks/watchlists/watchlists-mobile-v1-approved.md</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Created by PIA-GOV-004 (DEC-GOV-004 LOCKED)</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15934,6 +16011,33 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>Layout stability and premium feel with thin data payloads (AI Intelligence V2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEC-GOV-004</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Process Governance</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Approved Mock Preservation &amp; Design Lock Traceability: every Design Lock must archive the approved mock under docs/mocks/&lt;feature&gt;/APPROVED_&lt;feature&gt;_v&lt;version&gt;.png and COMMIT it to git BEFORE implementation starts; record the approved-mock path in the backlog item, UAT ticket, and Design Lock notes. Process: Requirement -&gt; UX Mockup -&gt; Design Review -&gt; Design Lock -&gt; SAVE approved mock -&gt; COMMIT approved mock -&gt; Implementation -&gt; UAT. Every UAT report must include Approved Mock &lt;path&gt;, Design Lock Commit &lt;id&gt;, Implementation Commit &lt;id&gt;. Non-compliance: implementation started without an archived approved mock is a governance violation and is blocked until the mock is committed.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Analyst Targets drifted because the approved mock was not preserved as a repository source of truth (PIA-GOV-004).</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2243,6 +2243,50 @@
       <c r="D22" t="inlineStr">
         <is>
           <t>PIA-GOV-004 Approved Mock Preservation &amp; Design Lock Traceability LOCKED (DEC-GOV-004); compliance audit + GOV-004-REMEDIATION created</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1b7d426</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AiIntelligenceCompactV3 premium compact widget (ARTEMIS-AI-COMPACT-REDESIGN-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3887882</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Compact V3 card customization + semantic tones (CR-AI-COMPACT-REDESIGN-002/003)</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M274"/>
+  <dimension ref="A1:M278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14449,12 +14493,277 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
           <t>Created by PIA-GOV-004 (DEC-GOV-004 LOCKED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-COMPACT-REDESIGN-001</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>AI Intelligence Compact V3</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AiIntelligenceCompactV3 premium compact widget: 3 rows x 4 cards, 2.2 visible cards per row; no Last Updated, no score badge, no dots/arrows</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Locked Compact V3 design</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Commit 1b7d426</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CR-AI-COMPACT-REDESIGN-002</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>AI Intelligence Compact V3</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Card customization: show/hide, drag reorder, three-dot Customize AI Cards sheet; persisted preferences</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Card source pool + customization framework</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Commit 3887882</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CR-AI-COMPACT-REDESIGN-003</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>AI Intelligence Compact V3</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Semantic tone engine: tone drives card border colour, icon glow, mini-chart stroke; Level High=red, Low=green; a BUY widget may contain red cards</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Semantic card coloring</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Commit 3887882</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CR-AI-COMPACT-V3-UAT</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Stock Intelligence</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>AI Intelligence Compact V3</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>UAT PASS decision pending: NVDA BUY / NBIS HOLD / AAPL HOLD widget + customize screenshots captured (390/430)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Screenshots: frontend/uat-screenshots/cr-ai-compact-v3-cr002/</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>PENDING UAT</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>APOLLO / PO</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>PENDING PASS DECISION</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Awaiting PO PASS decision</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16038,6 +16347,33 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>Analyst Targets drifted because the approved mock was not preserved as a repository source of truth (PIA-GOV-004).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DEC-AI-CV3</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AI Intelligence Compact V3 design lock principles: (1) no Last Updated; (2) no score badge; (3) no dots/arrows; (4) 3 rows; (5) 4 cards per row; (6) 2.2 visible cards per row; (7) card customization (show/hide, reorder, persisted); (8) semantic card coloring (tone -&gt; border/glow/chart stroke).</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Approved Compact V3 redesign; commits 1b7d426, 3887882</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2287,6 +2287,28 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>Compact V3 card customization + semantic tones (CR-AI-COMPACT-REDESIGN-002/003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GOV-021</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2 governance refresh: DEC-AI-009/010/011 LOCKED; HERMES-AI-005/006 COMPLETE; ARTEMIS-AI-011 IN PROGRESS; CR-AI-011 OPEN; HERMES-AI-007 + CR-HERMES-006-01 BACKLOG; RC pending UAT</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14766,6 +14788,380 @@
           <t>Awaiting PO PASS decision</t>
         </is>
       </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>HERMES-AI-005</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Shared Intelligence Context Layer: context aggregation, context endpoints, validation suite, coverage validation</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Backend foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>HERMES-AI-006</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Cache policy, source freshness metadata, frontend contract lock, example payloads, contract validation, frontend lightweight contract mode</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Perf warm 6ms compact / 9ms expanded; cold AAPL 2822 NVDA 2446 AMD 1919 TSM 1924 PLTR 1887 ms</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Contract ready for frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-011</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2 full implementation (Compact + Expanded) + shared hero</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Frontend ~80%</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>Commits 4982058,32a7814,8a1b579</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CR-AI-011</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Visual parity: expanded V2 UX fixes + compact layout overflow; pixel-match approved design</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Release blocker</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>Commit e67952f; release-blocking</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>HERMES-AI-007</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Parallel Context Hydration: reduce cold symbol load via parallel provider execution. Current 1.9-2.8s; target &lt;1.5s</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>BACKLOG</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>Cold-load optimization</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CR-HERMES-006-01</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Contract Versioning: introduce schemaVersion/contractVersion inside frontendPayload</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Contract evolution</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>BACKLOG</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F216">
@@ -15450,7 +15846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16374,6 +16770,87 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>Approved Compact V3 redesign; commits 1b7d426, 3887882</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DEC-AI-009</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Shared Intelligence Data Layer: AI Intelligence SHALL consume data exclusively through the Shared Intelligence Context Layer; direct provider access from widgets is prohibited. Consumers: AI Intelligence, Analyst Targets, Company, Financials, News, Videos.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Avoid duplicate fetch logic; consistency; centralized caching + validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DEC-AI-010</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AI Verdict Separation: AI Verdict (BUY/HOLD/SELL) and Portfolio Recommendation (ADD/HOLD/TRIM/REDUCE/AVOID) are independent systems. Compact shows AI Verdict only; Expanded may display portfolio recommendation.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Separate market verdict from portfolio-position action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DEC-AI-011</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hero System Standardization: all AI Intelligence states use shared hero assets (Neon Wireframe SVG, lattice geometry, institutional/premium look). Rejected: solid-fill, mascot, cartoon, emoji. Compact and Expanded must use identical hero assets.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>One premium hero visual language across compact + expanded.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2309,6 +2309,28 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>AI Intelligence V2 governance refresh: DEC-AI-009/010/011 LOCKED; HERMES-AI-005/006 COMPLETE; ARTEMIS-AI-011 IN PROGRESS; CR-AI-011 OPEN; HERMES-AI-007 + CR-HERMES-006-01 BACKLOG; RC pending UAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GOV-022</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research documentation: HERMES-AI-V3-001/002/003 COMPLETE; CR-AI-V3-UI-001 CLOSED (89bad3a); ARTEMIS-AI-V3-RESEARCH-003 IMPLEMENTED but approved mock MISSING; DEC-AI-RESEARCH-001..007 LOCKED; epics/bugs added</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M284"/>
+  <dimension ref="A1:M296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15103,9 +15125,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J283" t="inlineStr"/>
-      <c r="K283" t="inlineStr"/>
-      <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
           <t>Cold-load optimization</t>
@@ -15158,10 +15177,734 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>HERMES-AI-V3-001</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Research Backend Gap Analysis (coverage matrix for 9 sections, data-source mapping, proposed contract, provider gaps, thesis-only constraint)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Artifact: docs/HERMES-AI-V3-001_RESEARCH_BACKEND_GAP_ANALYSIS.md</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Backend-only audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>HERMES-AI-V3-002</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Research Endpoint V1: ai_research.py + GET /api/intelligence/{symbol}/research; thesis-only; explicit null/status placeholders</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>p50 9.93ms / p95 11.86ms; contract validator + example payload</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>No Buy/Hold/Sell; no portfolio action</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>HERMES-AI-V3-003</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Research Provenance &amp; Real Data Upgrade: schema V3.0, ResearchMetric + section provenance, competitiveComparison shouldRender=false when no provider; auditable null placeholders</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>p50 12.12ms / p95 17.29ms (well under 500/1000ms)</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>ACCEPTED</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>No dummy/fallback peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>CR-AI-V3-UI-001</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Overview/Compact/Expanded Hero corrections (C1-3, E1-7, S1-2: remove case badge, hero sizing, risk label, section header standard, breakpoints)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Corrected deviation from approved mock</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>Commit 89bad3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-V3-RESEARCH-003</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Research V2 final implementation (Research tab full impl + proxy route)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>GOVERNANCE GAP: approved mock research-approved.png is MISSING; Design Lock Package invalid (DESIGN-LOCK-002)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (LOCK INVALID)</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>BLOCKED - missing approved mock</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>Commits 8657868, b056bc1; needs approved-asset commit + UAT screenshots</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>EPIC-AI-RESEARCH-V2</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Institutional Research Memo: 11 sections, customization, provenance, real backend data only</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Dep: HERMES-AI-V3-003 done; ARTEMIS-AI-V3-RESEARCH-003</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>ARTEMIS / HERMES</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>Success: 390px matches mock; no dummy data; &lt;1s load; customizable</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>EPIC-AI-PROVENANCE</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Data Provenance &amp; Trust Layer: section + metric provenance, source/lastUpdated/refresh/confidence/dataType/calcMethod</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Backend V1 done in HERMES-AI-V3-003; frontend rendering pending Research V2</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>BACKEND COMPLETE</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>HERMES / ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>Frontend pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>EPIC-AI-COMPETITIVE-COMPARISON</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Competitive Comparison Engine: real peer-based comparison; no hardcoded/dummy/fallback peers; shouldRender=false if provider unavailable</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Backend placeholder only; future peer-selection provider</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>BACKLOG</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>Future provider work</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>BUG-HERMES-AI-007-AMD-MATERIAL-NEWS</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>AI Intelligence V2.5</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Older HERMES-AI-007 validator fails on AMD (material news impact missing); not caused by Research V1/V3; does not block Research endpoint</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>V2.5 dynamic news acceptance path</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Found during HERMES-AI-V3-002 regression</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BUG-AI-RESEARCH-COMPETITIVE-DATA-MISSING</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Competitive Comparison cannot render real peers (no peer/metrics provider); correctly returns status=missing, shouldRender=false</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Known gap; not blocking Research V2 UI when hidden</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>KNOWN GAP</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Needs peer provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>BUG-AI-RESEARCH-PROVIDER-GAPS</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>AI Intelligence V3 Research</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Missing providers: normalized financials, TAM/segment, revenue-vs-estimate, guidance, institutional ownership trends, fund sentiment, DCF; explicit null/status placeholders</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Known gap; explicit auditable placeholders</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>KNOWN GAP</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>Provider integration future</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>GOV-022-RESEARCH-MOCK-MISSING</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Mock Compliance</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Approved Research mock missing: research-approved.png absent (and typo research-aproved.png + drafts no longer present). Archive the approved image under docs/mocks/ai-intelligence/APPROVED/ and add RESEARCH_DESIGN_SPEC.md to validate the Research V2 Design Lock.</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Blocks UAT/closure of ARTEMIS-AI-V3-RESEARCH-003</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>ATHENA / PO</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-005 reference currently broken</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F216">
@@ -15846,7 +16589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16851,6 +17594,195 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>One premium hero visual language across compact + expanded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-001</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Research tab is thesis-only; it must not show Buy/Hold/Sell recommendation logic.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Research explains the thesis; verdict lives in Overview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ownership split: Overview owns verdict/action; Portfolio owns position action; Research owns thesis/deep analysis.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Clear separation of concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-003</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No dummy data allowed; missing provider data must be shown as missing/partial or hidden.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Auditable, trustworthy research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-004</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Competitive Comparison must only render with real backend-supported peer data (shouldRender=true).</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No hardcoded/dummy/fallback peers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-005</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Research V2 approved mock is docs/mocks/ai-intelligence/APPROVED/research-approved.png (implementation source of truth). WARNING: asset currently MISSING from repo — reference broken; Design Lock Package INVALID per DESIGN-LOCK-002 until the approved image is committed.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LOCKED (ASSET MISSING)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Asset must be archived/committed to validate the lock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-006</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Accordion arrows: collapsed = down arrow, expanded = up arrow (down encourages expansion).</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Affordance for deep-dive expansion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DEC-AI-RESEARCH-007</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Research customization locked: show/hide sections, drag reorder, text size S/M/L/XL, default expanded state, persist preferences.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Institutional-style configurable research.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,6 +2331,24 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>AI Intelligence V3 Research documentation: HERMES-AI-V3-001/002/003 COMPLETE; CR-AI-V3-UI-001 CLOSED (89bad3a); ARTEMIS-AI-V3-RESEARCH-003 IMPLEMENTED but approved mock MISSING; DEC-AI-RESEARCH-001..007 LOCKED; epics/bugs added</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>IBKR live portfolio modes + snapshot persistence; UAT screenshots under frontend/uat-screenshots/pia-ibkr-live-007/</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M296"/>
+  <dimension ref="A1:M297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13990,31 +14008,6 @@
         </is>
       </c>
     </row>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -15559,7 +15552,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
           <t>PENDING</t>
@@ -15622,9 +15614,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J291" t="inlineStr"/>
-      <c r="K291" t="inlineStr"/>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>Frontend pending</t>
@@ -15677,9 +15666,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J292" t="inlineStr"/>
-      <c r="K292" t="inlineStr"/>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
           <t>Future provider work</t>
@@ -15732,9 +15718,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J293" t="inlineStr"/>
-      <c r="K293" t="inlineStr"/>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
           <t>Found during HERMES-AI-V3-002 regression</t>
@@ -15787,9 +15770,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr"/>
-      <c r="K294" t="inlineStr"/>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
           <t>Needs peer provider</t>
@@ -15842,9 +15822,6 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J295" t="inlineStr"/>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
           <t>Provider integration future</t>
@@ -15897,12 +15874,76 @@
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr"/>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>DEC-AI-RESEARCH-005 reference currently broken</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-LIVE-007</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>IBKR live portfolio correctness + 3-mode source selection</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Mock / last-update / ibkr-live persisted across settings, provider status, live endpoints, and mobile/desktop source badges; deduped live positions; live snapshots persist locally.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>UAT screenshots: frontend/uat-screenshots/pia-ibkr-live-007/</t>
         </is>
       </c>
     </row>
@@ -16589,7 +16630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17783,6 +17824,33 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>Institutional-style configurable research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DEC-PORTFOLIO-MODE-001</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>data_source.mode is authoritative for portfolio source; ibkr.mode is transport-only.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Prevents mock/last-update from being overridden by IBKR integration settings; keeps provider status and portfolio endpoints aligned.</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18973,6 +19041,48 @@
       <c r="H69" t="inlineStr">
         <is>
           <t>Carried from 2026-06-02 watchlist UAT; still open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-LIVE-007</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Switch mock / last-update / ibkr-live and render mobile dashboard</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Each mode persists and renders the correct source badge/data; live snapshots persist locally.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Screenshots: frontend/uat-screenshots/pia-ibkr-live-007/</t>
         </is>
       </c>
     </row>
@@ -19413,7 +19523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20212,6 +20322,48 @@
       <c r="H22" t="inlineStr">
         <is>
           <t>PO UAT; choose Finnhub/FMP for firm-level target history if required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-LIVE-007</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>IBKR live portfolio correctness and 3-mode portfolio sync</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Align settings, provider status, live endpoints, snapshots, and mobile/desktop source badges.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / VALIDATED</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>py_compile + npm build + UAT screenshots PASS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PO review pending</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -2340,7 +2340,11 @@
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dedbf1e</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>HERMES</t>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2353,6 +2353,28 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>IBKR live portfolio modes + snapshot persistence; UAT screenshots under frontend/uat-screenshots/pia-ibkr-live-007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>IBKR live source resolution hardening; snapshot history, dedupe, option normalization, and strict provider/status contracts</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M297"/>
+  <dimension ref="A1:M298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15948,6 +15970,73 @@
       <c r="M297" t="inlineStr">
         <is>
           <t>UAT screenshots: frontend/uat-screenshots/pia-ibkr-live-007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-UAT-009</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>IBKR live data correctness, source switching, option handling, snapshot history, and status reporting</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Strict LIVE / LAST_UPDATE / DISCONNECTED reporting, no silent mock fallback, option normalization, duplicate detection, snapshot history, and shared source fields across provider/status/portfolio routes.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>Gateway offline during validation; live mode resolved to LAST_UPDATE; no mock leakage.</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19087,6 +19176,48 @@
       <c r="H70" t="inlineStr">
         <is>
           <t>Screenshots: frontend/uat-screenshots/pia-ibkr-live-007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-UAT-009</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Switch mock / last-update / ibkr-live; verify strict status, dedupe, option metadata, and history route</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>No duplicate positions; status reflects LIVE / LAST_UPDATE / DISCONNECTED; no mock leakage; history contract available</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Gateway offline in validation environment; live mode resolved to LAST_UPDATE; dedupe and option metadata verified from snapshot.</t>
         </is>
       </c>
     </row>
@@ -19527,7 +19658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20368,6 +20499,48 @@
       <c r="H23" t="inlineStr">
         <is>
           <t>PO review pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-UAT-009</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>IBKR live data correctness, source switching, option handling, snapshot history, and status reporting</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Portfolio state machine hardening, live/history persistence, option normalization, and strict source fields</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>py_compile + npm build + route smoke + provider mode checks</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PO UAT when authenticated IBKR Gateway is available</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2375,28 @@
       <c r="D28" t="inlineStr">
         <is>
           <t>IBKR live source resolution hardening; snapshot history, dedupe, option normalization, and strict provider/status contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Portfolio asset class normalization across mock, snapshot, live, and manual holdings; manual schema expansion for option metadata</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M298"/>
+  <dimension ref="A1:M299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16037,6 +16059,73 @@
       <c r="M298" t="inlineStr">
         <is>
           <t>Gateway offline during validation; live mode resolved to LAST_UPDATE; no mock leakage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-ASSETCLASS-001</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Explicit asset classification for stock, option, and crypto</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Normalize mock, snapshot, live, and manual holdings to assetClass values STK/OPT/CRYPTO and persist option metadata on manual holdings.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>assetClass exposed on portfolio rows and manual holdings schema expanded.</t>
         </is>
       </c>
     </row>
@@ -17961,7 +18050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19218,6 +19307,48 @@
       <c r="H71" t="inlineStr">
         <is>
           <t>Gateway offline in validation environment; live mode resolved to LAST_UPDATE; dedupe and option metadata verified from snapshot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-ASSETCLASS-001</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Normalize stock / option / crypto classification across portfolio sources</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>assetClass, expiry, strike, callPut, and contractDesc available on portfolio rows; crypto symbols normalize to CRYPTO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Backend compile plus API smoke checks; live gateway not needed for classification verification.</t>
         </is>
       </c>
     </row>
@@ -19658,7 +19789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20541,6 +20672,48 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>PO UAT when authenticated IBKR Gateway is available</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-ASSETCLASS-001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Asset class normalization</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Extend portfolio model and manual holdings schema for STK/OPT/CRYPTO classification</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>py_compile + API payload checks</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PO UAT when needed</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,6 +2397,28 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>Portfolio asset class normalization across mock, snapshot, live, and manual holdings; manual schema expansion for option metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>e57902c</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>IBKR live refresh + option classification hotfix</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16126,6 +16148,73 @@
       <c r="M299" t="inlineStr">
         <is>
           <t>assetClass exposed on portfolio rows and manual holdings schema expanded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-HOTFIX-010</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C300" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t>IBKR live refresh + option classification hotfix</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t>Live refresh cadence was sticky, options could inherit stock-like metadata, and mode switches could show stale status/data; fix contract-first classification, live cache invalidation, refresh metadata, and no-store cache headers.</t>
+        </is>
+      </c>
+      <c r="F300" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G300" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H300" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I300" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J300" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K300" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L300" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M300" s="1" t="inlineStr">
+        <is>
+          <t>Live gateway validation pending in this environment.</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19349,6 +19438,48 @@
       <c r="H72" t="inlineStr">
         <is>
           <t>Backend compile plus API smoke checks; live gateway not needed for classification verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-HOTFIX-010</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>Wait 30s in live mode and switch mock / last-update / live</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>Live data should refresh within the polling window; options stay in Options; mode changes invalidate stale live bundles; provider/status endpoints do not cache old state.</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>Backend validation passed; screenshots captured under frontend/uat-screenshots/ibkr-hotfix-010/.</t>
         </is>
       </c>
     </row>
@@ -19789,7 +19920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20714,6 +20845,48 @@
       <c r="H25" t="inlineStr">
         <is>
           <t>PO UAT when needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-HOTFIX-010</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>IBKR live refresh and option classification hotfix</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Shorten live cache TTL, invalidate caches on mode change, surface refresh metadata, and classify option rows from contract text before raw secType.</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + classification checks PASS</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>PO review pending; live-gateway evidence still pending.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2419,28 @@
       <c r="D30" s="1" t="inlineStr">
         <is>
           <t>IBKR live refresh + option classification hotfix</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-CONNECTIVITY-MISMATCH-017: fixed dual-stack localhost heartbeat timeout; added transport diagnostics/logging; restored IBKR_LIVE quote refresh.</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M300"/>
+  <dimension ref="A1:M301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14078,6 +14100,31 @@
         </is>
       </c>
     </row>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -16215,6 +16262,73 @@
       <c r="M300" s="1" t="inlineStr">
         <is>
           <t>Live gateway validation pending in this environment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-CONNECTIVITY-MISMATCH-017</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>Fix authenticated IBKR Gateway connectivity mismatch</t>
+        </is>
+      </c>
+      <c r="E301" s="1" t="inlineStr">
+        <is>
+          <t>Prefer IPv4 loopback for backend Gateway transport, log startup/request configuration, expose connectivity diagnostics, and restore live quote refresh.</t>
+        </is>
+      </c>
+      <c r="F301" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G301" s="1" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H301" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I301" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J301" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K301" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L301" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M301" s="1" t="inlineStr">
+        <is>
+          <t>docs/HERMES-IBKR-CONNECTIVITY-MISMATCH-017.md</t>
         </is>
       </c>
     </row>
@@ -16901,7 +17015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18122,6 +18236,33 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>Prevents mock/last-update from being overridden by IBKR integration settings; keeps provider status and portfolio endpoints aligned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DEC-IBKR-CONNECTIVITY-001</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Portfolio / IBKR</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Keep localhost as the user-facing Gateway configuration but prefer 127.0.0.1 for backend loopback transport unless IBKR_PREFER_IPV4=false.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Avoids the dual-stack localhost delay that exceeded the 2-second heartbeat timeout while retaining explicit environment overrides.</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19021,6 +19162,46 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -19480,6 +19661,48 @@
       <c r="H73" s="1" t="inlineStr">
         <is>
           <t>Backend validation passed; screenshots captured under frontend/uat-screenshots/ibkr-hotfix-010/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-CONNECTIVITY-MISMATCH-017</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>Compare localhost/127.0.0.1 and HTTP/HTTPS; validate authenticated connectivity, provider LIVE status, and four quote refresh intervals.</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>Gateway connected; source IBKR_LIVE; quote timestamps and values refresh; portfolio summary recalculates.</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>AMD 546.89 -&gt; 546.64 -&gt; 546.50 -&gt; 546.29 with advancing 12-14 second quote timestamps.</t>
         </is>
       </c>
     </row>
@@ -19920,7 +20143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -20887,6 +21110,48 @@
       <c r="H26" s="1" t="inlineStr">
         <is>
           <t>PO review pending; live-gateway evidence still pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-CONNECTIVITY-MISMATCH-017</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>Resolve IBKR Gateway connectivity mismatch</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Transport configuration/logging, connectivity endpoint, IPv4 loopback correction, frontend proxy, and live refresh validation.</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>py_compile, frontend build, backend/proxy routes, four live refresh intervals</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>Product Owner UAT</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2441,6 +2441,28 @@
       <c r="D31" s="1" t="inlineStr">
         <is>
           <t>HERMES-IBKR-CONNECTIVITY-MISMATCH-017: fixed dual-stack localhost heartbeat timeout; added transport diagnostics/logging; restored IBKR_LIVE quote refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024: identified port mismatch, missing polling/TFA refresh, stale-cache handoff, and duplicate Next hydration failure; added UI refresh diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M301"/>
+  <dimension ref="A1:M302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16329,6 +16351,73 @@
       <c r="M301" s="1" t="inlineStr">
         <is>
           <t>docs/HERMES-IBKR-CONNECTIVITY-MISMATCH-017.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>Live Portfolio Delivery</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>Diagnose frontend refresh lifecycle and TFA transition failure</t>
+        </is>
+      </c>
+      <c r="E302" s="1" t="inlineStr">
+        <is>
+          <t>Trace provider-to-React delivery, cache interaction, WebSocket/polling contract, Setup authentication lifecycle, and local dev-server integrity.</t>
+        </is>
+      </c>
+      <c r="F302" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G302" s="1" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H302" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I302" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J302" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K302" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L302" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M302" s="1" t="inlineStr">
+        <is>
+          <t>Diagnostic complete. Implementation continuation remains P0 OPEN. See docs/HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024.md</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18263,6 +18352,33 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>Avoids the dual-stack localhost delay that exceeded the 2-second heartbeat timeout while retaining explicit environment overrides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DEC-UI-REFRESH-001</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Frontend Data Delivery</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Use one shared HTTP/WS runtime config, WebSocket reconnect, 10-12 second polling fallback, and 2-second pending-TFA polling.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Removes hard-coded port divergence and ensures live state progresses when sockets or external authentication events do not notify React.</t>
         </is>
       </c>
     </row>
@@ -18280,7 +18396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19706,6 +19822,48 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Frontend / Portfolio</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>Observe mobile/desktop refresh without F5, dashboard cache handoff, WebSocket frames, and Setup TFA status checks.</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Identify exact stale layer with timestamps and runtime evidence.</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>Mobile: 1 dashboard request/18s, 0 socket frames, &gt;3m quote lag. Desktop: 0 responses from port 8000. Setup: 1 request/10s, no poll. Duplicate Next servers also caused chunk 404/hydration failure.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20143,7 +20301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21152,6 +21310,48 @@
       <c r="H27" s="1" t="inlineStr">
         <is>
           <t>Product Owner UAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>Diagnose live frontend refresh and TFA lifecycle</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Add refresh-status diagnostics, timestamp instrumentation, browser/cache/socket evidence, root-cause report, and continuation pack.</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>DIAGNOSTIC COMPLETE / FIX OPEN</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>py_compile, frontend build, API freshness, Playwright mobile/desktop/setup traces, WebSocket probes</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>Implement shared runtime config, reconnect/poll fallback, and Setup auth polling.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,6 +2463,28 @@
       <c r="D32" s="1" t="inlineStr">
         <is>
           <t>HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024: identified port mismatch, missing polling/TFA refresh, stale-cache handoff, and duplicate Next hydration failure; added UI refresh diagnostics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025: shared API/WS config, reconnecting dashboard stream, ten-second polling fallback, stale retry, and two-second TFA polling.</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M302"/>
+  <dimension ref="A1:M303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16418,6 +16440,73 @@
       <c r="M302" s="1" t="inlineStr">
         <is>
           <t>Diagnostic complete. Implementation continuation remains P0 OPEN. See docs/HERMES-FRONTEND-REFRESH-DIAGNOSTIC-024.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025</t>
+        </is>
+      </c>
+      <c r="B303" s="1" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C303" s="1" t="inlineStr">
+        <is>
+          <t>Live Portfolio Delivery</t>
+        </is>
+      </c>
+      <c r="D303" s="1" t="inlineStr">
+        <is>
+          <t>Implement automatic live refresh recovery</t>
+        </is>
+      </c>
+      <c r="E303" s="1" t="inlineStr">
+        <is>
+          <t>Shared API/WS config, socket reconnect, ten-second polling fallback, stale-cache follow-up, and two-second pending-TFA polling.</t>
+        </is>
+      </c>
+      <c r="F303" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G303" s="1" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H303" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I303" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J303" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K303" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L303" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M303" s="1" t="inlineStr">
+        <is>
+          <t>Controlled browser UAT PASS; Product Owner real-device/live-Gateway UAT pending.</t>
         </is>
       </c>
     </row>
@@ -18373,12 +18462,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>IMPLEMENTED</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Removes hard-coded port divergence and ensures live state progresses when sockets or external authentication events do not notify React.</t>
+          <t>Shared runtime config and resilient WebSocket/poll/TFA lifecycle shipped in HERMES-LIVE-REFRESH-FIX-025.</t>
         </is>
       </c>
     </row>
@@ -18396,7 +18485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19864,6 +19953,48 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Frontend / Portfolio</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>Verify no-F5 updates, socket reconnect, no-frame fallback, stale retry, and TFA transition</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>Mobile/Desktop update from socket; stale cache followed by fresh fetch; ten-second poll; Setup Ready within two seconds.</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>Mobile/Desktop $202 from second frame; stale/poll $100-&gt;$200-&gt;$300; reconnect connections=2; TFA Ready in 2248 ms. Screenshots archived.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20301,7 +20432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21352,6 +21483,48 @@
       <c r="H28" s="1" t="inlineStr">
         <is>
           <t>Implement shared runtime config, reconnect/poll fallback, and Setup auth polling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>Implement frontend live refresh recovery</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Central config, shared dashboard lifecycle, reconnect, poll fallback, stale retry, Setup/TFA polling, UAT evidence.</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>py_compile, tsc, production build, Playwright mobile/desktop/setup UAT</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>Product Owner real-device UAT with Gateway authenticated</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2485,6 +2485,28 @@
       <c r="D33" s="1" t="inlineStr">
         <is>
           <t>HERMES-LIVE-REFRESH-FIX-025: shared API/WS config, reconnecting dashboard stream, ten-second polling fallback, stale retry, and two-second TFA polling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4a15052</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>live position metrics mapping and score provenance hardening</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M303"/>
+  <dimension ref="A1:M304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14144,31 +14166,6 @@
         </is>
       </c>
     </row>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -16507,6 +16504,73 @@
       <c r="M303" s="1" t="inlineStr">
         <is>
           <t>Controlled browser UAT PASS; Product Owner real-device/live-Gateway UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-MAPPING-036</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Live position metrics mapping and score provenance hardening</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Day change / day P&amp;L / day P&amp;L% now derive from validated quote fields; risk and momentum come from cached AI intelligence when available; news score stays null until real scoring exists; stock hero prefers live quote cache.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>Backend tests pass; local long-lived Gateway-connected process was unavailable during validation in this workspace.</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19995,6 +20059,48 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-MAPPING-036</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Verify live metrics mapping, risk / momentum provenance, and stock hero quote contract</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Day change and P&amp;L should derive from quote fields; placeholder scores should not render as real metrics; stock hero should prefer the live portfolio quote cache.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PASS WITH CR</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Backend py_compile and unittest pass; direct local endpoint checks in this workspace still reflected the last-update fallback path because the long-lived Gateway-connected process was unavailable here. Implementation commit 4a15052.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20432,7 +20538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21528,6 +21634,48 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TASK-HERMES-S2C-METRICS-036</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Live position metrics mapping hardening</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Quote-field day metrics, score provenance, and stock hero contract</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4a15052 DONE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>py_compile + unittest PASS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Backlog/UAT/CHANGELOG synced</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -21542,7 +21690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -21589,7 +21737,7 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Analyst Targets V2 validation / Mobile UAT</t>
+          <t>Sprint 2C execution and UAT failure remediation / live position metrics mapping</t>
         </is>
       </c>
     </row>
@@ -21762,14 +21910,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Design Governance</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>LOCKED 2026-05-28: Mock-first development is mandatory; approved mocks must be stored under docs/design-system/mocks/ before UI implementation.</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Live position metrics mapping</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DONE 2026-06-23: Removed placeholder 55/70/50 metrics from live stock surfaces; risk/momentum provenance now comes from cached AI intelligence; stock hero reads live quote cache.</t>
         </is>
       </c>
     </row>
@@ -21788,36 +21936,36 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Design Governance</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>DONE 2026-05-28: Hybrid mock intelligence data layer v0.3.6 deployed. 9 tickers with company, fundamentals, ratios, earnings, targets, technical levels. IREN in positions, AVAV+TSLA in watchlist.</t>
+          <t>LOCKED 2026-05-28: Mock-first development is mandatory; approved mocks must be stored under docs/design-system/mocks/ before UI implementation.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Runtime Governance</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>LOCKED 2026-05-28 (v0.3.15): Single Next Dev Server Rule — only one Next dev server may run; check port 3000 first; kill stale node/next/npm and delete frontend/.next before restart; start LAN-bound (npm run dev -- -H 0.0.0.0); never run npm run build against a live dev server's .next; unstyled mobile = suspect stale/corrupt .next (404 CSS chunk), not UI code.</t>
+          <t>DONE 2026-05-28: Hybrid mock intelligence data layer v0.3.6 deployed. 9 tickers with company, fundamentals, ratios, earnings, targets, technical levels. IREN in positions, AVAV+TSLA in watchlist.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Workspace Manager</t>
+          <t>Runtime Governance</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
+          <t>LOCKED 2026-05-28 (v0.3.15): Single Next Dev Server Rule — only one Next dev server may run; check port 3000 first; kill stale node/next/npm and delete frontend/.next before restart; start LAN-bound (npm run dev -- -H 0.0.0.0); never run npm run build against a live dev server's .next; unstyled mobile = suspect stale/corrupt .next (404 CSS chunk), not UI code.</t>
         </is>
       </c>
     </row>
@@ -21829,29 +21977,41 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; Settings/About are accessible; all/overflow workspaces can open directly; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
+          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
+          <t>Workspace Manager</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-05-28 (v0.3.15): Mobile top-left hamburger opens Workspace Manager; Settings/About are accessible; all/overflow workspaces can open directly; bottom nav uses pia.workspaces.pinnedMobile capped at five; desktop sidebar uses pia.workspaces.sidebarDesktop; custom workspaces persist in pia.workspaces.custom; shared order persists in pia.workspaces.order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
           <t>Mobile Regression Fix</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>DONE 2026-05-28 (v0.3.16): Global search universe expanded (AAPL/MSFT/AMZN/META/SPY/QQQ/+ v0.3.6 set) with Enter-to-open and Analyze fallback; per-ticker mock news fallback (generate_mock_news) so every symbol shows source-badged news; used_demo only true for demo/mock, false for real Yahoo. Hamburger menu satisfied by v0.3.15 Workspace Manager.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Release Reference</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>v0.3.18 Portfolio Mobile Card V2: PIA-UX-032 DONE 2026-05-30. Owner ARTEMIS.</t>
         </is>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,28 @@
       <c r="D34" t="inlineStr">
         <is>
           <t>live position metrics mapping and score provenance hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>4a15052</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>research data and live contract hardening</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M304"/>
+  <dimension ref="A1:M305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16571,6 +16593,73 @@
       <c r="M304" t="inlineStr">
         <is>
           <t>Backend tests pass; local long-lived Gateway-connected process was unavailable during validation in this workspace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>HERMES-RESEARCH-DATA-AND-LIVE-CONTRACT-040</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Research / Portfolio</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>AI Intelligence / Portfolio</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Research data and live contract hardening</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Research payloads now return explicit missing sections and provenance; live portfolio positions expose metricStates / missingMetrics; null-safe risk handling prevents live route crashes.</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>Fresh backend validation passed on AMD and NBIS research payloads; live portfolio route returns explicit metric-state metadata.</t>
         </is>
       </c>
     </row>
@@ -18549,7 +18638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19431,46 +19520,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -20098,6 +20147,48 @@
       <c r="H77" t="inlineStr">
         <is>
           <t>Backend py_compile and unittest pass; direct local endpoint checks in this workspace still reflected the last-update fallback path because the long-lived Gateway-connected process was unavailable here. Implementation commit 4a15052.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>HERMES-RESEARCH-DATA-AND-LIVE-CONTRACT-040</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Research / Portfolio</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Validate AMD/NBIS research payloads and live portfolio contract</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Research payloads should expose explicit missing sections/provenance; live portfolio contract should expose metricStates/missingMetrics and not crash on null risk.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>PASS WITH CR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Fresh backend validation passed; frontend not modified; PO UAT still pending.</t>
         </is>
       </c>
     </row>
@@ -20538,7 +20629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21671,6 +21762,48 @@
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>Backlog/UAT/CHANGELOG synced</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TASK-HERMES-RESEARCH-040</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Research data and live contract hardening</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Research payload contract + live portfolio metric state metadata</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4a15052 DONE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>py_compile + unittest PASS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Backlog/UAT/CHANGELOG synced</t>
         </is>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2529,6 +2529,28 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>research data and live contract hardening</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>b684469</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041: stabilized live mobile refresh rendering, preserved component identity across polls, and added remount/loading diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:M306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16660,6 +16682,73 @@
       <c r="M305" t="inlineStr">
         <is>
           <t>Fresh backend validation passed on AMD and NBIS research payloads; live portfolio route returns explicit metric-state metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Mobile / Portfolio</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Mobile live refresh blink stabilization</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Keep live mobile dashboard state stable across polls, memoize portfolio sections, preserve last live positions, and add remount diagnostics so live prices update in place without full-screen blink.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>Build pass in frontend; PO UAT pending; commit b684469.</t>
         </is>
       </c>
     </row>
@@ -18638,7 +18727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20189,6 +20278,48 @@
       <c r="H78" t="inlineStr">
         <is>
           <t>Fresh backend validation passed; frontend not modified; PO UAT still pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Frontend / Mobile</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Observe mobile portfolio live updates for 60s without remount or global loading flash.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Prices update in place; no full-screen blink; scroll/tab state persists.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Build passed; dev-only remount/loading diagnostics added; PO UAT pending.</t>
         </is>
       </c>
     </row>
@@ -20629,7 +20760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21809,6 +21940,48 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Stabilize mobile live refresh rendering</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Stable dashboard merge, memoized sections, live-row preservation, diagnostics</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>b684469 DONE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>npm run build PASS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PO UAT and evidence capture</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -21823,7 +21996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -22147,6 +22320,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>v0.3.18 Portfolio Mobile Card V2: PIA-UX-032 DONE 2026-05-30. Owner ARTEMIS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Mobile Live Refresh Blink Stabilization</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-06-23 (HERMES): live mobile refresh preserves component identity across polls, memoizes section shells, and keeps the last non-empty live portfolio rows to prevent mock fallback flashes. Build passed; PO UAT pending.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2551,6 +2551,28 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041: stabilized live mobile refresh rendering, preserved component identity across polls, and added remount/loading diagnostics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-QUOTES-037: aligned live quote propagation across hero, AI context, and position table; extended live quote debug contract.</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M306"/>
+  <dimension ref="A1:M307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16749,6 +16771,73 @@
       <c r="M306" t="inlineStr">
         <is>
           <t>Build pass in frontend; PO UAT pending; commit b684469.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-QUOTES-037</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Backend / Frontend</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Live Portfolio Delivery</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Real-time IBKR quote propagation</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Keep hero, AI context, and position table aligned to the same live dashboard quote seed; extend live-quotes diagnostics with explicit counters and timestamps.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>Backend live quote diagnostics and frontend live-seed precedence fixed; PO UAT pending.</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20320,6 +20409,48 @@
       <c r="H79" t="inlineStr">
         <is>
           <t>Build passed; dev-only remount/loading diagnostics added; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-QUOTES-037</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Backend / Frontend</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Observe live quote propagation across portfolio, hero, and AI context without refresh.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Quote timestamps advance and hero / table use identical live source.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Debug live-quotes and stock payload inspection confirmed advancing quote timestamps; hero seed precedence fixed.</t>
         </is>
       </c>
     </row>
@@ -20760,7 +20891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21982,6 +22113,48 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-QUOTES-037</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Align live quote propagation across UI consumers</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Backend debug contract, frontend live-seed precedence, shared live quote source</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>backend live debug inspection + frontend build</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Commit and push after docs sync</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -21996,7 +22169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -22332,6 +22505,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>IMPLEMENTED 2026-06-23 (HERMES): live mobile refresh preserves component identity across polls, memoizes section shells, and keeps the last non-empty live portfolio rows to prevent mock fallback flashes. Build passed; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Live Quote Propagation Alignment</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-06-23 (HERMES): live quote debug endpoint now reports source, quote count, and latest timestamp; stock hero follows the live dashboard seed for held positions so it stays aligned with the table.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2573,6 +2573,28 @@
       <c r="D37" t="inlineStr">
         <is>
           <t>HERMES-LIVE-QUOTES-037: aligned live quote propagation across hero, AI context, and position table; extended live quote debug contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-038: recompute live day P/L and unrealized from quote inputs, sum daily P/L from positions, and add calculation provenance.</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M307"/>
+  <dimension ref="A1:M308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14232,6 +14254,31 @@
         </is>
       </c>
     </row>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -16838,6 +16885,73 @@
       <c r="M307" t="inlineStr">
         <is>
           <t>Backend live quote diagnostics and frontend live-seed precedence fixed; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-038</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>Live position metric recalculation and provenance</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t>Recompute day P/L, day %, unrealized, and portfolio daily P/L from validated live quote inputs; expose calculation provenance in live/debug payloads.</t>
+        </is>
+      </c>
+      <c r="F308" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G308" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H308" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I308" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J308" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K308" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L308" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M308" s="1" t="inlineStr">
+        <is>
+          <t>Backend regression tests cover stock, option, mixed portfolio, nullable-input, and summary aggregation cases; live Gateway validation pending.</t>
         </is>
       </c>
     </row>
@@ -18816,7 +18930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19698,6 +19812,46 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -20329,51 +20483,51 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>HERMES-RESEARCH-DATA-AND-LIVE-CONTRACT-040</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-038</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Research / Portfolio</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Validate AMD/NBIS research payloads and live portfolio contract</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Research payloads should expose explicit missing sections/provenance; live portfolio contract should expose metricStates/missingMetrics and not crash on null risk.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>PASS WITH CR</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio / Live Metrics</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>Day P/L and unrealized recalculation</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>Day P/L, day %, unrealized, and portfolio daily P/L derive from live quote inputs without fake zero fallback values.</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Fresh backend validation passed; frontend not modified; PO UAT still pending.</t>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>Backend regression tests passed; live Gateway validation pending in this workspace.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041</t>
+          <t>HERMES-RESEARCH-DATA-AND-LIVE-CONTRACT-040</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -20383,22 +20537,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frontend / Mobile</t>
+          <t>Research / Portfolio</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Observe mobile portfolio live updates for 60s without remount or global loading flash.</t>
+          <t>Validate AMD/NBIS research payloads and live portfolio contract</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Prices update in place; no full-screen blink; scroll/tab state persists.</t>
+          <t>Research payloads should expose explicit missing sections/provenance; live portfolio contract should expose metricStates/missingMetrics and not crash on null risk.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LOCAL PASS</t>
+          <t>PASS WITH CR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -20408,47 +20562,89 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Build passed; dev-only remount/loading diagnostics added; PO UAT pending.</t>
+          <t>Fresh backend validation passed; frontend not modified; PO UAT still pending.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Frontend / Mobile</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Observe mobile portfolio live updates for 60s without remount or global loading flash.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Prices update in place; no full-screen blink; scroll/tab state persists.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Build passed; dev-only remount/loading diagnostics added; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>HERMES-LIVE-QUOTES-037</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Backend / Frontend</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Observe live quote propagation across portfolio, hero, and AI context without refresh.</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Quote timestamps advance and hero / table use identical live source.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>LOCAL PASS</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Debug live-quotes and stock payload inspection confirmed advancing quote timestamps; hero seed precedence fixed.</t>
         </is>
@@ -20891,7 +21087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22152,6 +22348,48 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>Commit and push after docs sync</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-038</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Fix live day P/L and unrealized calculations</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Live position metric recalculation, nullable outputs, summary aggregation, and calculation provenance.</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>pending commit in this branch</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest pass</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>Commit and push after docs/workbook sync</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2595,6 +2595,28 @@
       <c r="D38" s="1" t="inlineStr">
         <is>
           <t>HERMES-LIVE-POSITION-METRICS-038: recompute live day P/L and unrealized from quote inputs, sum daily P/L from positions, and add calculation provenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>live price provider fallback when ibkr is disconnected</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M308"/>
+  <dimension ref="A1:M309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14254,31 +14276,6 @@
         </is>
       </c>
     </row>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -16952,6 +16949,73 @@
       <c r="M308" s="1" t="inlineStr">
         <is>
           <t>Backend regression tests cover stock, option, mixed portfolio, nullable-input, and summary aggregation cases; live Gateway validation pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-PRICE-PROVIDER-FALLBACK-044</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>Live price provider fallback when IBKR disconnects</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="inlineStr">
+        <is>
+          <t>Keep last-known IBKR positions while overlaying Yahoo Finance fallback prices and recalc market value, day P/L, unrealized, and portfolio total.</t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G309" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H309" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I309" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J309" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K309" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L309" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M309" s="1" t="inlineStr">
+        <is>
+          <t>Ready for PO UAT; live Gateway validation pending in this workspace.</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19812,46 +19876,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -20647,6 +20671,48 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>Debug live-quotes and stock payload inspection confirmed advancing quote timestamps; hero seed precedence fixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-PRICE-PROVIDER-FALLBACK-044</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio prices keep updating when IBKR is disconnected</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo fallback prices overlay the latest IBKR snapshot positions</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>Added Yahoo Finance fallback pricing and hybrid portfolio source metadata; live Gateway UAT is still pending.</t>
         </is>
       </c>
     </row>
@@ -21087,7 +21153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22393,6 +22459,44 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-PRICE-PROVIDER-FALLBACK-044</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>feat: add live price provider fallback when ibkr is disconnected</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest + frontend build PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>Ready for PO UAT</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22407,7 +22511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -22454,7 +22558,7 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>Sprint 2C execution and UAT failure remediation / live position metrics mapping</t>
+          <t>Sprint 2C execution and UAT failure remediation / live position metrics mapping / live price provider fallback</t>
         </is>
       </c>
     </row>
@@ -22755,6 +22859,18 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>IMPLEMENTED 2026-06-23 (HERMES): live quote debug endpoint now reports source, quote count, and latest timestamp; stock hero follows the live dashboard seed for held positions so it stays aligned with the table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Live price provider fallback</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-06-23 (HERMES): Yahoo Finance fallback pricing keeps the portfolio moving when IBKR is disconnected; last-known positions are preserved and portfolio mode exposes hybrid state.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2617,6 +2617,28 @@
       <c r="D39" s="1" t="inlineStr">
         <is>
           <t>live price provider fallback when ibkr is disconnected</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048: durable snapshot lifecycle, startup warm-up, explicit no-data state, and snapshot debug/status contracts.</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M309"/>
+  <dimension ref="A1:M310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17016,6 +17038,73 @@
       <c r="M309" s="1" t="inlineStr">
         <is>
           <t>Ready for PO UAT; live Gateway validation pending in this workspace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>IBKR snapshot lifecycle persistence and hybrid fallback</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="inlineStr">
+        <is>
+          <t>Preserve the latest valid IBKR portfolio snapshot with refresh-state metadata/history, seed startup warm-up, expose snapshot debug/status contracts, and return explicit NO_DATA when neither live nor snapshot data exists.</t>
+        </is>
+      </c>
+      <c r="F310" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G310" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H310" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest PASS</t>
+        </is>
+      </c>
+      <c r="K310" s="1" t="inlineStr">
+        <is>
+          <t>Ready for PO UAT</t>
+        </is>
+      </c>
+      <c r="L310" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M310" s="1" t="inlineStr">
+        <is>
+          <t>Durable snapshot saves, startup warm-up, snapshot refresh metadata, and explicit no-data fallback; local validation passed 2026-06-24.</t>
         </is>
       </c>
     </row>
@@ -18994,7 +19083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20713,6 +20802,48 @@
       <c r="H82" s="1" t="inlineStr">
         <is>
           <t>Added Yahoo Finance fallback pricing and hybrid portfolio source metadata; live Gateway UAT is still pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio / Snapshot Lifecycle</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>Persist live IBKR snapshots, warm startup cache, and fall back to the latest snapshot or NO_DATA.</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Valid live snapshots persist; failed or empty refreshes do not overwrite good data; snapshot debug/status fields expose refresh state; no-data state is explicit.</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>py_compile and unittest passed; PO UAT pending.</t>
         </is>
       </c>
     </row>
@@ -21153,7 +21284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22497,6 +22628,48 @@
       </c>
       <c r="H35" s="1" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Persist IBKR snapshots and expose snapshot lifecycle status</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Durable snapshot saves, startup warm-up, snapshot debug/status contracts, and explicit no-data fallback.</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>pending commit in this branch</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest pass</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>Commit, push, and await PO UAT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22511,7 +22684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -22871,6 +23044,18 @@
       <c r="B32" s="1" t="inlineStr">
         <is>
           <t>IMPLEMENTED 2026-06-23 (HERMES): Yahoo Finance fallback pricing keeps the portfolio moving when IBKR is disconnected; last-known positions are preserved and portfolio mode exposes hybrid state.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>IBKR Snapshot Lifecycle Persistence</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-06-24 (HERMES): durable IBKR snapshots now preserve the last valid bundle, startup warm-up seeds the live cache, and the portfolio stack reports explicit NO_DATA when neither live nor snapshot data exists. Build passed; PO UAT pending.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,6 +2639,292 @@
       <c r="D40" s="1" t="inlineStr">
         <is>
           <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048: durable snapshot lifecycle, startup warm-up, explicit no-data state, and snapshot debug/status contracts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>current branch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PRICE-PROVIDER-FALLBACK-UX-045: badge variants hybrid subtitle dual timestamps stale banner position source markers settings split. npm run build PASS 11.2s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ATHENA-DOCS-SYNC-049</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ATHENA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ATHENA-DOCS-SYNC-049: docs sync — UAT outcomes recorded; open P0s registered: HERMES-PORTFOLIO-CALCULATION-046, HERMES-LIVE-QUOTES-037, HERMES-LIVE-REFRESH-039, ARTEMIS-PORTFOLIO-TABLE-COLUMNS-047.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>8a9d43b0 FAIL-UAT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048: FAIL PO UAT — lifecycle not as required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>a27ba55/3374c7d PARTIAL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>HERMES-PRICE-PROVIDER-FALLBACK-044: PARTIAL PO UAT — Yahoo fallback done; snapshot persistence not matching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>b684469/dfd7335 FAIL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041: FAIL PO UAT — flashing reduced; calcs wrong; quotes not propagating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4a15052/a38becd FAIL</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-MAPPING-036: FAIL PO UAT — portfolio calcs still incorrect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>current branch PARTIAL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-RESEARCH-TAB-IMPLEMENTATION-038: PARTIAL PO UAT — V3 visible; backend gaps; object bug; card nesting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>9d20e03</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>HERMES-RESEARCH-DATA-AND-LIVE-CONTRACT-040: READY FOR UAT — explicit missing states; null-risk handling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>current branch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-MARKETDATA-STATUS-028: IMPLEMENTED — C5.10 prefix parse fix; field mapping 85/86.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>current branch</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ARTEMIS-SETTINGS-DATASOURCE-UX-018: IMPLEMENTED — Portfolio Data Source card; gateway validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>current branch</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PIA-IBKR-APP-SWITCH-027: IMPLEMENTED — pageshow + TFA polling + auto refresh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3c4a4b6</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025: IMPLEMENTED — shared API_BASE_URL/WS_BASE_URL; WebSocket reconnect; 10s polling; TFA polling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-RECOVERY-052: restore production-grade portfolio source lifecycle and compact settings source display.</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16672,7 +16958,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>FAIL PO UAT</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -16692,7 +16978,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>LOCAL PASS</t>
+          <t>FAIL - portfolio calcs still incorrect</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -16739,7 +17025,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>READY FOR UAT</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -16759,7 +17045,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>LOCAL PASS</t>
+          <t>READY FOR UAT - local pass, commit 9d20e03</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -16806,7 +17092,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>FAIL PO UAT</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -16826,7 +17112,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FAIL - flashing reduced; calcs wrong; quotes not propagating</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -16940,7 +17226,7 @@
       </c>
       <c r="G308" s="1" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>FAIL PO UAT</t>
         </is>
       </c>
       <c r="H308" s="1" t="inlineStr">
@@ -16960,7 +17246,7 @@
       </c>
       <c r="K308" s="1" t="inlineStr">
         <is>
-          <t>LOCAL PASS</t>
+          <t>FAIL - calcs still wrong</t>
         </is>
       </c>
       <c r="L308" s="1" t="inlineStr">
@@ -17007,7 +17293,7 @@
       </c>
       <c r="G309" s="1" t="inlineStr">
         <is>
-          <t>IMPLEMENTED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H309" s="1" t="inlineStr">
@@ -17027,7 +17313,7 @@
       </c>
       <c r="K309" s="1" t="inlineStr">
         <is>
-          <t>LOCAL PASS</t>
+          <t>PARTIAL - snapshot persistence not matching requirements</t>
         </is>
       </c>
       <c r="L309" s="1" t="inlineStr">
@@ -17074,37 +17360,560 @@
       </c>
       <c r="G310" s="1" t="inlineStr">
         <is>
+          <t>FAIL PO UAT</t>
+        </is>
+      </c>
+      <c r="H310" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J310" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest PASS</t>
+        </is>
+      </c>
+      <c r="K310" s="1" t="inlineStr">
+        <is>
+          <t>FAIL - lifecycle not behaving as required</t>
+        </is>
+      </c>
+      <c r="L310" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M310" s="1" t="inlineStr">
+        <is>
+          <t>Durable snapshot saves, startup warm-up, snapshot refresh metadata, and explicit no-data fallback; local validation passed 2026-06-24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-CALCULATION-046</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Fix portfolio calculations</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Portfolio Total, Day P/L, Day P/L %, Unrealized P/L incorrect. Root cause TBD.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>OPEN P0</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-039</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Full dashboard refresh architecture</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>End-to-end refresh audit covering polling, WS, stale cache, and live-mode consistency.</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>OPEN P0</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PORTFOLIO-TABLE-COLUMNS-047</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Portfolio table columns ordering sorting desktop parity</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Add missing columns, correct ordering, fix sorting, achieve desktop-mobile parity.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>OPEN P0</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PRICE-PROVIDER-FALLBACK-UX-045</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Price provider fallback UI</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Badge variants, hybrid subtitle, dual timestamps, stale banner, position source markers, settings split.</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>READY FOR UAT</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>PASS - npm run build 11.2s</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>PENDING PO UAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ARTEMIS-SETTINGS-DATASOURCE-UX-018</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>IBKR Live</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Portfolio Data Source settings card</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Mock/Last Update/Live IBKR selector; auto gateway validation; live status indicators.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
           <t>IMPLEMENTED</t>
         </is>
       </c>
-      <c r="H310" s="1" t="inlineStr">
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PIA-IBKR-APP-SWITCH-027</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>IBKR Live</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>IBKR app switch auto-refresh</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>pageshow listener, TFA polling, auto dashboard refresh on IBKR app return.</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-MARKETDATA-STATUS-028</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>IBKR Live</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>IBKR market data prefix parse fix</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Support C5.10-style prefix values; correct field mapping 85/86; restore pricesLive.</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
         <is>
           <t>HERMES</t>
         </is>
       </c>
-      <c r="I310" s="1" t="inlineStr">
+      <c r="I317" t="inlineStr">
         <is>
           <t>feat/pia-v3-foundation-integration</t>
         </is>
       </c>
-      <c r="J310" s="1" t="inlineStr">
-        <is>
-          <t>py_compile + unittest PASS</t>
-        </is>
-      </c>
-      <c r="K310" s="1" t="inlineStr">
-        <is>
-          <t>Ready for PO UAT</t>
-        </is>
-      </c>
-      <c r="L310" s="1" t="inlineStr">
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-RESEARCH-TAB-IMPLEMENTATION-038</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>ResearchTabV3 implementation</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>14 modules, SVG charts, 30 PD definitions, missing data shows dash. Wired into StockAiIntelligenceWidget.</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>ARTEMIS</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>PARTIAL - backend gaps, object bug, card nesting</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-RECOVERY-052</t>
+        </is>
+      </c>
+      <c r="B319" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D319" s="1" t="inlineStr">
+        <is>
+          <t>IBKR source lifecycle recovery</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t>Restore live IBKR detection and automatic source switching across settings, provider status, portfolio, dashboard, and mobile; keep snapshot/demo fallback automatic and surface compact source state only.</t>
+        </is>
+      </c>
+      <c r="F319" s="1" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G319" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="H319" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I319" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="J319" s="1" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K319" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="L319" s="1" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="M310" s="1" t="inlineStr">
-        <is>
-          <t>Durable snapshot saves, startup warm-up, snapshot refresh metadata, and explicit no-data fallback; local validation passed 2026-06-24.</t>
+      <c r="M319" s="1" t="inlineStr">
+        <is>
+          <t>Runtime source resolution now matches live Gateway heartbeat; compact settings card shows Current Source / Last Updated.</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20844,6 +21653,510 @@
       <c r="H83" s="1" t="inlineStr">
         <is>
           <t>py_compile and unittest passed; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PRICE-PROVIDER-FALLBACK-UX-045</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Portfolio / UI</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Badge variant, subtitle, timestamps, stale banner, source markers</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Correct variants; stale banner; per-position markers; settings split</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>LOCAL PASS (npm run build)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>PENDING PO UAT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>resolvePortfolioBadge + resolvePositionPriceSource; MobileStatusDock; Settings non-fatal gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-SNAPSHOT-LIFECYCLE-048-UAT</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Portfolio / Snapshot</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>PO UAT of snapshot lifecycle</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Lifecycle as required</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FAIL PO UAT</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Commit 8a9d43b0 - still not matching requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HERMES-PRICE-PROVIDER-FALLBACK-044-UAT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PO UAT of price provider fallback</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Yahoo fallback + hybrid correct</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PARTIAL PO UAT</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Commits a27ba55/3374c7d - snapshot persistence not matching</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>HERMES-MOBILE-LIVE-REFRESH-BLINK-041-UAT</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Mobile / Live</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PO UAT of mobile live refresh blink fix</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>No flashing; correct calcs</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FAIL PO UAT</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Commits b684469/dfd7335 - calcs wrong; quotes not propagating</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-POSITION-METRICS-MAPPING-036-UAT</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Portfolio / Metrics</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PO UAT of live position metrics mapping</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Day P/L Day % Unrealized correct</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>FAIL PO UAT</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Commits 4a15052/a38becd - portfolio calcs still incorrect</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ARTEMIS-AI-RESEARCH-TAB-038-UAT</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AI Intelligence</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PO UAT of ResearchTabV3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Research V3 renders with correct data</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>PARTIAL PO UAT</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>V3 visible; backend gaps; [object Object] bug; card nesting; missing analyst dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HERMES-RESEARCH-DATA-CONTRACT-040</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AI Intelligence / Backend</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Research data contract hardening local validation</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Explicit missing states; null-safe routes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>PENDING PO UAT</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Commit 9d20e03</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-MARKETDATA-STATUS-028</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Portfolio / IBKR</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>C5.10 prefix parse fix validation</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>pricesLive restored; field 85/86 correct</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Fixed prefix-value parse; field mapping; pricesLive flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ARTEMIS-SETTINGS-DATASOURCE-UX-018</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Portfolio Data Source card</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Mode selector gateway validation status indicators</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Mock/Last Update/Live IBKR; auto gateway validation on mode switch</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ARTEMIS-PIA-IBKR-APP-SWITCH-027</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Mobile / IBKR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Auto refresh on IBKR app return</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Refresh triggered; TFA polling resolves</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>pageshow + TFA polling + auto dashboard refresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>HERMES-LIVE-REFRESH-FIX-025</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Frontend / Live</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Shared API_BASE_URL WS reconnect polling fallback</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>No stale data; reconnects on socket close</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Commit 3c4a4b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-RECOVERY-052</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio / Source Lifecycle</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>Confirm provider status, portfolio, dashboard, and mobile all resolve to Live IBKR when Gateway is authenticated</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>Settings, provider status, portfolio endpoints, dashboard, and mobile should agree on IBKR_LIVE with automatic snapshot/demo fallback</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>Runtime provider status now uses the live heartbeat path and the compact settings card shows Current Source / Last Updated.</t>
         </is>
       </c>
     </row>
@@ -21284,7 +22597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22670,6 +23983,48 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>HERMES-IBKR-RECOVERY-052</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Restore production-grade portfolio source lifecycle</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Runtime provider status, source resolver sync, snapshot/demo fallback, compact settings source card</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED / LOCAL PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>py_compile + unittest + npm build PASS</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>Commit and push after docs sync</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -22684,7 +24039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -23056,6 +24411,18 @@
       <c r="B33" s="1" t="inlineStr">
         <is>
           <t>IMPLEMENTED 2026-06-24 (HERMES): durable IBKR snapshots now preserve the last valid bundle, startup warm-up seeds the live cache, and the portfolio stack reports explicit NO_DATA when neither live nor snapshot data exists. Build passed; PO UAT pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>IBKR Source Lifecycle Recovery</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED 2026-06-24 (HERMES): runtime source detection now resolves live IBKR from the heartbeat path, so settings, portfolio, dashboard, and mobile all agree on the current source contract.</t>
         </is>
       </c>
     </row>

--- a/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
+++ b/docs/PIA_MASTER_BACKLOG_SOURCE_OF_TRUTH.xlsx
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,28 @@
       <c r="D53" s="1" t="inlineStr">
         <is>
           <t>HERMES-IBKR-RECOVERY-052: restore production-grade portfolio source lifecycle and compact settings source display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pending commit</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-PRODUCTION-062: MarketDataEngine, conid-first option pricing, canonical snapshot artifact, portfolio reconciliation endpoint, quote-cache diagnostics.</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14584,6 +14606,31 @@
         </is>
       </c>
     </row>
+    <row r="241"/>
+    <row r="242"/>
+    <row r="243"/>
+    <row r="244"/>
+    <row r="245"/>
+    <row r="246"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
+    <row r="250"/>
+    <row r="251"/>
+    <row r="252"/>
+    <row r="253"/>
+    <row r="254"/>
+    <row r="255"/>
+    <row r="256"/>
+    <row r="257"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
@@ -17914,6 +17961,73 @@
       <c r="M319" s="1" t="inlineStr">
         <is>
           <t>Runtime source resolution now matches live Gateway heartbeat; compact settings card shows Current Source / Last Updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-PRODUCTION-062</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Portfolio Production Stabilization</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>MarketDataEngine + Canonical Portfolio DTO</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Separate market data from portfolio calculations; enforce conid-first option quotes; add reconciliation and quote-cache diagnostics; persist canonical price-free snapshot artifact.</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>READY FOR PO UAT</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>python py_compile PASS; backend unittest discovery PASS (28); frontend build PASS</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>PO must validate against live IBKR app during market/extended-hours session.</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>HERMES-062</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19875,6 +19989,33 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>Shared runtime config and resilient WebSocket/poll/TFA lifecycle shipped in HERMES-LIVE-REFRESH-FIX-025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DEC-PORTFOLIO-MARKETDATA-001</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Portfolio Engine</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>All portfolio state must originate from the Canonical Portfolio DTO. Market prices must flow through MarketDataEngine / Quote Cache. Options must resolve quotes by conid; fallback to underlying stock symbols is prohibited.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prevents UI-specific calculations, stale quote confusion, and option mispricing.</t>
         </is>
       </c>
     </row>
@@ -19892,7 +20033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20774,6 +20915,46 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -22157,6 +22338,48 @@
       <c r="H95" s="1" t="inlineStr">
         <is>
           <t>Runtime provider status now uses the live heartbeat path and the compact settings card shows Current Source / Last Updated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>UAT-HERMES-062</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Portfolio Production Engine</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MarketDataEngine, quote cache, option conid pricing, canonical snapshot, reconciliation diagnostics</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Desktop == Mobile == IBKR in live mode; snapshot + Yahoo fallback recalculates; reconciliation endpoint reports PASS; options are never priced from underlying.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>PENDING PO UAT</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Local validation passed: py_compile, 28 backend tests, frontend build. Live IBKR comparison requires PO market-session UAT.</t>
         </is>
       </c>
     </row>
@@ -22597,7 +22820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24025,6 +24248,48 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>HERMES-PORTFOLIO-PRODUCTION-062</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HERMES</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>feat/pia-v3-foundation-integration</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Complete production portfolio engine stabilization before AI Intelligence V4.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MarketDataEngine, Quote Cache, option conid guardrail, canonical DTO routing, price-free snapshot artifact, reconciliation endpoint, diagnostics.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>READY FOR PO UAT</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>py_compile PASS; unittest discovery PASS; npm build PASS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PO validate live IBKR reconciliation and extended-hours behavior.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -24039,7 +24304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -24423,6 +24688,18 @@
       <c r="B34" s="1" t="inlineStr">
         <is>
           <t>IMPLEMENTED 2026-06-24 (HERMES): runtime source detection now resolves live IBKR from the heartbeat path, so settings, portfolio, dashboard, and mobile all agree on the current source contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-06-29 HERMES-062</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Portfolio Production Engine READY FOR PO UAT: MarketDataEngine and Canonical DTO path implemented; live IBKR reconciliation pending PO validation.</t>
         </is>
       </c>
     </row>
